--- a/flight simulator ecosystem version 1.xlsx
+++ b/flight simulator ecosystem version 1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/PRO-G40/FSEI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E2B99FB-5085-2545-A9A2-1094513073D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{986DE58E-2809-3642-8E20-EA9F147A0E50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4420" yWindow="640" windowWidth="25820" windowHeight="19000" firstSheet="9" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="640" windowWidth="30240" windowHeight="19000" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard " sheetId="1" r:id="rId1"/>
@@ -18,30 +18,33 @@
     <sheet name="Manufacturers_DB" sheetId="21" r:id="rId3"/>
     <sheet name="---- AIRCRAFT ----" sheetId="22" r:id="rId4"/>
     <sheet name="Aircraft-db" sheetId="2" r:id="rId5"/>
-    <sheet name="Aircraft_Variants" sheetId="12" r:id="rId6"/>
-    <sheet name="Engines_DB" sheetId="13" r:id="rId7"/>
-    <sheet name="Variant-Engines" sheetId="14" r:id="rId8"/>
-    <sheet name="Aircraft_Configurations" sheetId="16" r:id="rId9"/>
-    <sheet name="Systems_Depth" sheetId="10" r:id="rId10"/>
-    <sheet name="Evaluation_Sources" sheetId="15" r:id="rId11"/>
-    <sheet name="---- AVIONICS ----" sheetId="24" r:id="rId12"/>
-    <sheet name="Avionics_DB" sheetId="17" r:id="rId13"/>
-    <sheet name="Configuration_Avionics" sheetId="18" r:id="rId14"/>
-    <sheet name="Avionics_Evaluations" sheetId="19" r:id="rId15"/>
-    <sheet name="Avionics_Evaluation_Sources" sheetId="20" r:id="rId16"/>
-    <sheet name="---- EVIDENCE ----" sheetId="25" r:id="rId17"/>
-    <sheet name="Sources_DB" sheetId="11" r:id="rId18"/>
-    <sheet name="---- SCENERY ----" sheetId="26" r:id="rId19"/>
-    <sheet name="Airport-db" sheetId="3" r:id="rId20"/>
-    <sheet name="---- DEVELOPERS ----" sheetId="27" r:id="rId21"/>
-    <sheet name="Developer-db" sheetId="4" r:id="rId22"/>
-    <sheet name="---- SCORING ----" sheetId="28" r:id="rId23"/>
-    <sheet name="Quarterly_data" sheetId="5" r:id="rId24"/>
-    <sheet name="Weight_Settings" sheetId="6" r:id="rId25"/>
-    <sheet name="Scoring_engine" sheetId="7" r:id="rId26"/>
-    <sheet name="Forecast " sheetId="8" r:id="rId27"/>
-    <sheet name="---- ADMIN ----" sheetId="29" r:id="rId28"/>
-    <sheet name="Documentation " sheetId="9" r:id="rId29"/>
+    <sheet name="Simulator_Products" sheetId="30" r:id="rId6"/>
+    <sheet name="Product_Developers" sheetId="31" r:id="rId7"/>
+    <sheet name="Product_Variants" sheetId="32" r:id="rId8"/>
+    <sheet name="Aircraft_Variants" sheetId="12" r:id="rId9"/>
+    <sheet name="Engines_DB" sheetId="13" r:id="rId10"/>
+    <sheet name="Variant-Engines" sheetId="14" r:id="rId11"/>
+    <sheet name="Aircraft_Configurations" sheetId="16" r:id="rId12"/>
+    <sheet name="Systems_Depth" sheetId="10" r:id="rId13"/>
+    <sheet name="Evaluation_Sources" sheetId="15" r:id="rId14"/>
+    <sheet name="---- AVIONICS ----" sheetId="24" r:id="rId15"/>
+    <sheet name="Avionics_DB" sheetId="17" r:id="rId16"/>
+    <sheet name="Configuration_Avionics" sheetId="18" r:id="rId17"/>
+    <sheet name="Avionics_Evaluations" sheetId="19" r:id="rId18"/>
+    <sheet name="Avionics_Evaluation_Sources" sheetId="20" r:id="rId19"/>
+    <sheet name="---- EVIDENCE ----" sheetId="25" r:id="rId20"/>
+    <sheet name="Sources_DB" sheetId="11" r:id="rId21"/>
+    <sheet name="---- SCENERY ----" sheetId="26" r:id="rId22"/>
+    <sheet name="Airport-db" sheetId="3" r:id="rId23"/>
+    <sheet name="---- DEVELOPERS ----" sheetId="27" r:id="rId24"/>
+    <sheet name="Developer-db" sheetId="4" r:id="rId25"/>
+    <sheet name="---- SCORING ----" sheetId="28" r:id="rId26"/>
+    <sheet name="Quarterly_data" sheetId="5" r:id="rId27"/>
+    <sheet name="Weight_Settings" sheetId="6" r:id="rId28"/>
+    <sheet name="Scoring_engine" sheetId="7" r:id="rId29"/>
+    <sheet name="Forecast " sheetId="8" r:id="rId30"/>
+    <sheet name="---- ADMIN ----" sheetId="29" r:id="rId31"/>
+    <sheet name="Documentation " sheetId="9" r:id="rId32"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dashboard '!$A$5:$A$7</definedName>
@@ -105,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="373">
   <si>
     <t xml:space="preserve">FSEI DASHBOARD </t>
   </si>
@@ -189,9 +192,6 @@
   </si>
   <si>
     <t>Aircraft</t>
-  </si>
-  <si>
-    <t>Developer</t>
   </si>
   <si>
     <t>Aircraft Type</t>
@@ -1022,9 +1022,6 @@
     <t>A321</t>
   </si>
   <si>
-    <t>Toliss</t>
-  </si>
-  <si>
     <t>A321-200</t>
   </si>
   <si>
@@ -1212,13 +1209,91 @@
   </si>
   <si>
     <t>ToLiss A321 GPS / Navigation System evaluated through direct simulator testing and official documentation. Demonstrated high-fidelity aircraft positioning, route and waypoint sequencing, SID/STAR and approach procedure handling, navigation-data processing, and integration with the FMGS, navigation display, and autoflight systems throughout the complete KCLT–KLAF evaluation flight. Normal navigation functionality was extensively demonstrated; degraded GPS, navigation-sensor failures, and unusual navigation edge cases remain candidates for additional direct testing.</t>
+  </si>
+  <si>
+    <t>Developer (Legacy)</t>
+  </si>
+  <si>
+    <t>Simulator (Legacy)</t>
+  </si>
+  <si>
+    <t>Simulator_Products</t>
+  </si>
+  <si>
+    <t>Product ID</t>
+  </si>
+  <si>
+    <t>Product Name</t>
+  </si>
+  <si>
+    <t>FlightFactor 777v2</t>
+  </si>
+  <si>
+    <t>XP12</t>
+  </si>
+  <si>
+    <t>FlightFactor 777v2 simulator aircraft product</t>
+  </si>
+  <si>
+    <t>ToLiss A321</t>
+  </si>
+  <si>
+    <t>Developer ID</t>
+  </si>
+  <si>
+    <t>Developer-db</t>
+  </si>
+  <si>
+    <t>Developer Name</t>
+  </si>
+  <si>
+    <t>Flight Simulator Aircraft Products</t>
+  </si>
+  <si>
+    <t>Product_Developers</t>
+  </si>
+  <si>
+    <t>Product Developer ID</t>
+  </si>
+  <si>
+    <t>Role</t>
+  </si>
+  <si>
+    <t>Primary Developer</t>
+  </si>
+  <si>
+    <t>Primary developer for FlightFactor 777v2 product</t>
+  </si>
+  <si>
+    <t>StepToSky</t>
+  </si>
+  <si>
+    <t>Flight simulation development partner</t>
+  </si>
+  <si>
+    <t>Development Partner</t>
+  </si>
+  <si>
+    <t>Development partner for FlightFactor 777v2 product</t>
+  </si>
+  <si>
+    <t>Developer of high-fidelity Airbus aircraft simulations for X-Plane.</t>
+  </si>
+  <si>
+    <t>ToLiss A321 simulator aircraft product</t>
+  </si>
+  <si>
+    <t>Product_Variants</t>
+  </si>
+  <si>
+    <t>Product Variant ID</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1343,6 +1418,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1366,7 +1449,7 @@
     <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1439,13 +1522,84 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="126">
+  <dxfs count="131">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -4252,43 +4406,107 @@
 </FeaturePropertyBags>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{3AE1B3D4-D00B-224E-ADA9-6812ECA37ACE}" name="tblManufacturers" displayName="tblManufacturers" ref="A3:B7" totalsRowShown="0" headerRowDxfId="114" dataDxfId="113">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{3AE1B3D4-D00B-224E-ADA9-6812ECA37ACE}" name="tblManufacturers" displayName="tblManufacturers" ref="A3:B7" totalsRowShown="0" headerRowDxfId="119" dataDxfId="118">
   <autoFilter ref="A3:B7" xr:uid="{3AE1B3D4-D00B-224E-ADA9-6812ECA37ACE}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{68EDBF10-6062-9E48-BBA7-9DF719EC8919}" name="Manufacturers ID" dataDxfId="112"/>
-    <tableColumn id="2" xr3:uid="{E24BEBDF-49CC-F244-AADE-5E70FA97BB64}" name="Manfacturer" dataDxfId="111"/>
+    <tableColumn id="1" xr3:uid="{68EDBF10-6062-9E48-BBA7-9DF719EC8919}" name="Manufacturers ID" dataDxfId="117"/>
+    <tableColumn id="2" xr3:uid="{E24BEBDF-49CC-F244-AADE-5E70FA97BB64}" name="Manfacturer" dataDxfId="116"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{2B8535B2-545D-B646-8144-39856DB386E9}" name="tblConfigurationAvionics" displayName="tblConfigurationAvionics" ref="A3:G20" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23">
-  <autoFilter ref="A3:G20" xr:uid="{2B8535B2-545D-B646-8144-39856DB386E9}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{72F6FEBC-05DA-4640-913D-5D4FDE46F951}" name="Configuration Avionics ID" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{DC1B7654-CC28-F54E-8CEA-6E265526895E}" name="Configuration ID" dataDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{2523EDBE-122F-244A-AC1A-C7C86771C3C1}" name="Avionics ID" dataDxfId="20"/>
-    <tableColumn id="8" xr3:uid="{57CA651E-454A-DB43-88C0-D22559B8941A}" name="Configuration Name" dataDxfId="19">
-      <calculatedColumnFormula>_xlfn.XLOOKUP(tblConfigurationAvionics[[#This Row],[Configuration ID]],tblAircraftConfigurations[Configuration ID],tblAircraftConfigurations[Configuration Name],"")</calculatedColumnFormula>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{63B5D24B-73F5-1641-866F-955C5B4232DF}" name="tblSystemsDepth" displayName="tblSystemsDepth" ref="A3:N7" totalsRowShown="0" headerRowDxfId="62" dataDxfId="61">
+  <autoFilter ref="A3:N7" xr:uid="{63B5D24B-73F5-1641-866F-955C5B4232DF}"/>
+  <tableColumns count="14">
+    <tableColumn id="12" xr3:uid="{71838FF8-8EA3-E145-839C-E770AD0A1825}" name="Evaluation ID" dataDxfId="60"/>
+    <tableColumn id="13" xr3:uid="{830E8BF7-B2BB-AA48-8DD3-7A53BCE99354}" name="Evaluation Sope" dataDxfId="59"/>
+    <tableColumn id="1" xr3:uid="{1CDFBD3B-AC1F-8E40-AD5A-7D32EB0461D8}" name="Aircraft ID" dataDxfId="58"/>
+    <tableColumn id="14" xr3:uid="{89E6CB87-B930-4D4B-9CFF-8F51F5B3D448}" name="Variant ID" dataDxfId="57"/>
+    <tableColumn id="15" xr3:uid="{1846A538-2482-4D4F-B0CD-625030C3A885}" name="Variant" dataDxfId="56">
+      <calculatedColumnFormula>IF(tblSystemsDepth[[#This Row],[Variant ID]]="","",_xlfn.XLOOKUP(tblSystemsDepth[[#This Row],[Variant ID]],tblAircraftVariants[Variant ID],tblAircraftVariants[Variant],""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{A24184C6-26A0-114A-80FB-7AD0F2F7F0EE}" name="Avionics System">
-      <calculatedColumnFormula>_xlfn.XLOOKUP(tblConfigurationAvionics[[#This Row],[Avionics ID]],tblAvionics[Avionics ID],tblAvionics[System / Model],"")</calculatedColumnFormula>
+    <tableColumn id="2" xr3:uid="{EFF66939-2B24-8942-AC75-55E8E3512C09}" name="Aircraft" dataDxfId="55">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(tblSystemsDepth[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Aircraft],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{8BD4B34D-0E4F-8B47-B72A-DB35A08E1C15}" name="Avionics Role" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{64A5A1E5-236C-CD43-9BBC-D30E2E797368}" name="Notes" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{1A3DB43D-D852-2F42-B2E3-BCD34D59544E}" name="Simulator" dataDxfId="54">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(tblSystemsDepth[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator (Legacy)],"")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{FD4E0C00-EB23-D643-ACDC-C68FE92C1F14}" name="Electrical Systems" dataDxfId="53"/>
+    <tableColumn id="5" xr3:uid="{D0D57CB5-2B06-BA41-87E1-9C741B94C9BA}" name="Hydraulic / Pneumatic Systems" dataDxfId="52"/>
+    <tableColumn id="6" xr3:uid="{104E682F-6DC8-854D-A154-5FBA7DEBB578}" name="FMS / Navigation Depth" dataDxfId="51"/>
+    <tableColumn id="7" xr3:uid="{AE16E340-1AC8-6C48-A766-6D329DEFEBE0}" name="Failures / Abnormal Procedures" dataDxfId="50"/>
+    <tableColumn id="8" xr3:uid="{64436D13-11E2-3743-8A88-349F63F3B07A}" name="Procedural Fidelity" dataDxfId="49"/>
+    <tableColumn id="9" xr3:uid="{FF6DA7CD-FDAF-2547-A6E9-9BF3BA532FE3}" name="Systems Depth Score" dataDxfId="48">
+      <calculatedColumnFormula>IF(COUNT(tblSystemsDepth[[#This Row],[Electrical Systems]]:tblSystemsDepth[[#This Row],[Procedural Fidelity]])=0,"",ROUND(SUM(tblSystemsDepth[[#This Row],[Electrical Systems]]:tblSystemsDepth[[#This Row],[Procedural Fidelity]])/(COUNT(tblSystemsDepth[[#This Row],[Electrical Systems]]:tblSystemsDepth[[#This Row],[Procedural Fidelity]])*20)*100,0))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="11" xr3:uid="{24257476-02E0-CC46-A27E-C70E64D998A8}" name="Date Verified" dataDxfId="47">
+      <calculatedColumnFormula>TODAY()</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{A343DC97-0181-E149-BD77-C60F4FFD7C37}" name="tblAvionicsEvaluations" displayName="tblAvionicsEvaluations" ref="A3:P20" totalsRowShown="0" headerRowDxfId="125">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{2C709437-1283-944D-BA35-6A0090DBFC2A}" name="tblEvaluationSources" displayName="tblEvaluationSources" ref="A3:G13" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45">
+  <autoFilter ref="A3:G13" xr:uid="{2C709437-1283-944D-BA35-6A0090DBFC2A}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{373931B1-12C6-EA45-9488-3CC9CC170B8A}" name="Evaluation Source ID" dataDxfId="44"/>
+    <tableColumn id="2" xr3:uid="{7A4336C9-AD77-5749-AD56-6746F090A352}" name="Evaluation ID" dataDxfId="43"/>
+    <tableColumn id="3" xr3:uid="{CC4C0828-0EFF-E94E-84AA-E2590D186F3E}" name="Source ID" dataDxfId="42"/>
+    <tableColumn id="6" xr3:uid="{19934B5E-6937-ED40-8637-7B3C0A0FCD04}" name="Aircraft" dataDxfId="41">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(tblEvaluationSources[[#This Row],[Evaluation ID]],tblSystemsDepth[Evaluation ID],tblSystemsDepth[Aircraft],"")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{8B58A9D1-5D0A-5A43-9F0D-FD63879B5104}" name="Source Name" dataDxfId="40">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(tblEvaluationSources[[#This Row],[Source ID]],tblSources[Source ID],tblSources[Source Name],"")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{C96A00CF-D76A-8D4D-937F-6484B2249F72}" name="Evidence Role" dataDxfId="39"/>
+    <tableColumn id="5" xr3:uid="{60EE9860-EE6C-5845-9129-4E5C6D8DA919}" name="Notes" dataDxfId="38"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{76DE734F-5104-7649-A8A0-8325D3E9D528}" name="tblAvionics" displayName="tblAvionics" ref="A3:F20" totalsRowShown="0" headerRowDxfId="37" dataDxfId="36">
+  <autoFilter ref="A3:F20" xr:uid="{76DE734F-5104-7649-A8A0-8325D3E9D528}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{8B02509B-77BE-A244-8E95-67E9875FD8A4}" name="Avionics ID" dataDxfId="35"/>
+    <tableColumn id="2" xr3:uid="{FAD56923-8BBD-E349-A02D-D480703FE180}" name="Developer / Manufacturer" dataDxfId="34"/>
+    <tableColumn id="3" xr3:uid="{702DD557-8925-8F4C-9C15-32A33EAA4453}" name="Avionics Type" dataDxfId="33"/>
+    <tableColumn id="4" xr3:uid="{FFA2D378-D7FA-7040-99E5-90F161F2D109}" name="System / Model" dataDxfId="32"/>
+    <tableColumn id="5" xr3:uid="{60CDEF54-08D6-714B-95D6-A1B24C928431}" name="Version / Generation" dataDxfId="31"/>
+    <tableColumn id="6" xr3:uid="{43E29A70-C46E-A54D-A76F-34E730126823}" name="Notes" dataDxfId="30"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{2B8535B2-545D-B646-8144-39856DB386E9}" name="tblConfigurationAvionics" displayName="tblConfigurationAvionics" ref="A3:G20" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
+  <autoFilter ref="A3:G20" xr:uid="{2B8535B2-545D-B646-8144-39856DB386E9}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{72F6FEBC-05DA-4640-913D-5D4FDE46F951}" name="Configuration Avionics ID" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{DC1B7654-CC28-F54E-8CEA-6E265526895E}" name="Configuration ID" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{2523EDBE-122F-244A-AC1A-C7C86771C3C1}" name="Avionics ID" dataDxfId="25"/>
+    <tableColumn id="8" xr3:uid="{57CA651E-454A-DB43-88C0-D22559B8941A}" name="Configuration Name" dataDxfId="24">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(tblConfigurationAvionics[[#This Row],[Configuration ID]],tblAircraftConfigurations[Configuration ID],tblAircraftConfigurations[Configuration Name],"")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{A24184C6-26A0-114A-80FB-7AD0F2F7F0EE}" name="Avionics System">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(tblConfigurationAvionics[[#This Row],[Avionics ID]],tblAvionics[Avionics ID],tblAvionics[System / Model],"")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{8BD4B34D-0E4F-8B47-B72A-DB35A08E1C15}" name="Avionics Role" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{64A5A1E5-236C-CD43-9BBC-D30E2E797368}" name="Notes" dataDxfId="22"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{A343DC97-0181-E149-BD77-C60F4FFD7C37}" name="tblAvionicsEvaluations" displayName="tblAvionicsEvaluations" ref="A3:P20" totalsRowShown="0" headerRowDxfId="130">
   <autoFilter ref="A3:P20" xr:uid="{A343DC97-0181-E149-BD77-C60F4FFD7C37}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{8FBED1AD-D88E-5947-A7A4-12DE42FF5BFE}" name="Avionics Evaluation ID"/>
@@ -4299,31 +4517,31 @@
     <tableColumn id="4" xr3:uid="{F0CAEB6E-F820-B144-998B-31651BE7C61E}" name="Avionics ID">
       <calculatedColumnFormula>_xlfn.XLOOKUP(B4,Configuration_Avionics!$A$4:$A$100,Configuration_Avionics!$C$4:$C$100,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{A09C8E0A-CCA0-FD4C-9E63-DCCFC4B7A25E}" name="Aircraft" dataDxfId="124">
+    <tableColumn id="5" xr3:uid="{A09C8E0A-CCA0-FD4C-9E63-DCCFC4B7A25E}" name="Aircraft" dataDxfId="129">
       <calculatedColumnFormula>_xlfn.XLOOKUP(C4,Aircraft_Configurations!$A$4:$A$100,Aircraft_Configurations!$D$4:$D$100,"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{B11A28DE-0D67-3149-8AF1-A8CEA9045300}" name="Avionics System ">
       <calculatedColumnFormula>_xlfn.XLOOKUP(D4,Avionics_DB!$A$4:$A$102,Avionics_DB!$D$4:$D$102,"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{509DF4ED-5CC4-0C4B-8144-F4F70E3B518C}" name="Evaluation Date "/>
-    <tableColumn id="10" xr3:uid="{5EC875F0-7D6F-9545-BE59-9B29524A46C5}" name="Functional Fidelity" dataDxfId="123"/>
-    <tableColumn id="11" xr3:uid="{8DD2FF07-0C2A-E54D-A54F-87D97B63A9FF}" name="Operational / Procedural Fidelity" dataDxfId="122"/>
-    <tableColumn id="12" xr3:uid="{D69480CC-DA01-D942-B5F0-8BEC1BDE1F44}" name="Display &amp; Interface Fidelity" dataDxfId="121"/>
-    <tableColumn id="13" xr3:uid="{3F3F6C11-F816-804C-91A2-2B403EAAD4BE}" name="System Logic &amp; Integration" dataDxfId="120"/>
-    <tableColumn id="14" xr3:uid="{28B631A1-62B6-3047-9034-1E8D890A7689}" name="Navigation Data Handling &amp; Implementation" dataDxfId="119"/>
-    <tableColumn id="15" xr3:uid="{213E0A02-04A3-FA43-A249-204073BCFBA2}" name="Failures &amp; Abnormal Behavior" dataDxfId="118"/>
-    <tableColumn id="16" xr3:uid="{ADB26855-09C2-7543-BB77-916C4F8BBA9F}" name="Depth &amp; Edge-Case Fidelity" dataDxfId="117"/>
-    <tableColumn id="8" xr3:uid="{5F09423E-F6A9-844B-95B0-7103B19643D1}" name="Fidelity Score" dataDxfId="116">
+    <tableColumn id="10" xr3:uid="{5EC875F0-7D6F-9545-BE59-9B29524A46C5}" name="Functional Fidelity" dataDxfId="128"/>
+    <tableColumn id="11" xr3:uid="{8DD2FF07-0C2A-E54D-A54F-87D97B63A9FF}" name="Operational / Procedural Fidelity" dataDxfId="127"/>
+    <tableColumn id="12" xr3:uid="{D69480CC-DA01-D942-B5F0-8BEC1BDE1F44}" name="Display &amp; Interface Fidelity" dataDxfId="126"/>
+    <tableColumn id="13" xr3:uid="{3F3F6C11-F816-804C-91A2-2B403EAAD4BE}" name="System Logic &amp; Integration" dataDxfId="125"/>
+    <tableColumn id="14" xr3:uid="{28B631A1-62B6-3047-9034-1E8D890A7689}" name="Navigation Data Handling &amp; Implementation" dataDxfId="124"/>
+    <tableColumn id="15" xr3:uid="{213E0A02-04A3-FA43-A249-204073BCFBA2}" name="Failures &amp; Abnormal Behavior" dataDxfId="123"/>
+    <tableColumn id="16" xr3:uid="{ADB26855-09C2-7543-BB77-916C4F8BBA9F}" name="Depth &amp; Edge-Case Fidelity" dataDxfId="122"/>
+    <tableColumn id="8" xr3:uid="{5F09423E-F6A9-844B-95B0-7103B19643D1}" name="Fidelity Score" dataDxfId="121">
       <calculatedColumnFormula>IF(COUNT(H4:N20)=0,"",ROUND(SUM(H4:N4)/(IF(H4&lt;&gt;"",25,0)+IF(I4&lt;&gt;"",20,0)+IF(J4&lt;&gt;"",15,0)+IF(K4&lt;&gt;"",20,0)+IF(L4&lt;&gt;"",8,0)+IF(M4&lt;&gt;"",7,0)+IF(N4&lt;&gt;"",5,0))*100,0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{2B3B11DB-BB8B-A34F-B0EA-0BB744A434B3}" name="Notes" dataDxfId="115"/>
+    <tableColumn id="9" xr3:uid="{2B3B11DB-BB8B-A34F-B0EA-0BB744A434B3}" name="Notes" dataDxfId="120"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
-<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{8C50C5A9-2C5B-8343-8439-12531C81D16A}" name="tblAvionicsEvaluationSources" displayName="tblAvionicsEvaluationSources" ref="A3:G15" totalsRowShown="0" headerRowDxfId="16">
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{8C50C5A9-2C5B-8343-8439-12531C81D16A}" name="tblAvionicsEvaluationSources" displayName="tblAvionicsEvaluationSources" ref="A3:G15" totalsRowShown="0" headerRowDxfId="21">
   <autoFilter ref="A3:G15" xr:uid="{8C50C5A9-2C5B-8343-8439-12531C81D16A}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{4324B45A-60DA-C949-8426-EC5975B68452}" name="Avionics Evaluation Source ID"/>
@@ -4342,206 +4560,191 @@
 </table>
 </file>
 
-<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{16599F6C-5ACD-8541-B49F-65461897A4D2}" name="tblSources" displayName="tblSources" ref="A3:N21" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{16599F6C-5ACD-8541-B49F-65461897A4D2}" name="tblSources" displayName="tblSources" ref="A3:N21" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <autoFilter ref="A3:N21" xr:uid="{16599F6C-5ACD-8541-B49F-65461897A4D2}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{57395D4B-7D02-FF45-A4B9-27F1D47064EC}" name="Source ID" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{326E8E84-323F-254E-8D41-F5BBA241BE95}" name="Aircraft ID" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{C05EF523-F7BD-FF4F-B652-86D05C0DA15C}" name="Variant ID" dataDxfId="11"/>
-    <tableColumn id="11" xr3:uid="{7B014AC4-D0EB-D04E-99F6-D4F87F486AAE}" name="Variant" dataDxfId="10">
+    <tableColumn id="1" xr3:uid="{57395D4B-7D02-FF45-A4B9-27F1D47064EC}" name="Source ID" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{326E8E84-323F-254E-8D41-F5BBA241BE95}" name="Aircraft ID" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{C05EF523-F7BD-FF4F-B652-86D05C0DA15C}" name="Variant ID" dataDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{7B014AC4-D0EB-D04E-99F6-D4F87F486AAE}" name="Variant" dataDxfId="15">
       <calculatedColumnFormula>IF(tblSources[[#This Row],[Variant ID]]="","",_xlfn.XLOOKUP(tblSources[[#This Row],[Variant ID]],tblAircraftVariants[Variant ID],tblAircraftVariants[Variant],""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{8B28D6FE-B428-F745-808D-E5912BC520E2}" name="Evidence Scope" dataDxfId="9"/>
-    <tableColumn id="12" xr3:uid="{82992551-182A-3E4A-86FB-B7BB0001832C}" name="Aircraft" dataDxfId="8">
+    <tableColumn id="14" xr3:uid="{8B28D6FE-B428-F745-808D-E5912BC520E2}" name="Evidence Scope" dataDxfId="14"/>
+    <tableColumn id="12" xr3:uid="{82992551-182A-3E4A-86FB-B7BB0001832C}" name="Aircraft" dataDxfId="13">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Aircraft],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{0C34BBAC-6A7B-B244-9450-5BA46933B3EA}" name="Simulator" dataDxfId="7">
-      <calculatedColumnFormula>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator],"")</calculatedColumnFormula>
+    <tableColumn id="13" xr3:uid="{0C34BBAC-6A7B-B244-9450-5BA46933B3EA}" name="Simulator" dataDxfId="12">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator (Legacy)],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{E2500407-807B-B942-9DED-0714DE4B2FE1}" name="Source Type" dataDxfId="6"/>
-    <tableColumn id="10" xr3:uid="{2631E2AD-159A-CD4C-9DB6-8C0BF0995881}" name="Source Name" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{FA3D63DC-0C2F-6A4C-A15E-BA4E0BD234D4}" name="Source URL" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{0B01A120-48DD-6B45-AB42-AF7F71075B36}" name="Date Assessed" dataDxfId="3">
+    <tableColumn id="3" xr3:uid="{E2500407-807B-B942-9DED-0714DE4B2FE1}" name="Source Type" dataDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{2631E2AD-159A-CD4C-9DB6-8C0BF0995881}" name="Source Name" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{FA3D63DC-0C2F-6A4C-A15E-BA4E0BD234D4}" name="Source URL" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{0B01A120-48DD-6B45-AB42-AF7F71075B36}" name="Date Assessed" dataDxfId="8">
       <calculatedColumnFormula>TODAY()</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{644763EE-4255-EF44-B94A-20C30CBF3E08}" name="Notes" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{6996E54E-E270-A94D-9024-E4EAA1B7914D}" name="Date Verified" dataDxfId="1">
+    <tableColumn id="7" xr3:uid="{644763EE-4255-EF44-B94A-20C30CBF3E08}" name="Notes" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{6996E54E-E270-A94D-9024-E4EAA1B7914D}" name="Date Verified" dataDxfId="6">
       <calculatedColumnFormula>TODAY()</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{AA4450E5-2E56-AB43-A629-E6859D75123D}" name="Active Source" dataDxfId="0"/>
+    <tableColumn id="9" xr3:uid="{AA4450E5-2E56-AB43-A629-E6859D75123D}" name="Active Source" dataDxfId="5"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{2C22E5EA-2502-7348-8B02-160174A0CB2D}" name="Table15" displayName="Table15" ref="A3:C6" totalsRowShown="0">
+  <autoFilter ref="A3:C6" xr:uid="{2C22E5EA-2502-7348-8B02-160174A0CB2D}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{DDB9B887-8D12-2842-BD1E-394A9FD24D17}" name="Developer ID"/>
+    <tableColumn id="2" xr3:uid="{8E53E313-88F9-C844-9E63-DB72EFD2B862}" name="Developer Name"/>
+    <tableColumn id="3" xr3:uid="{69CE64F4-8B8F-5944-A870-CB2F0AACC644}" name="Notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{29F43501-CD9F-B44B-A5D1-9D851BC153E9}" name="tblAircraft" displayName="tblAircraft" ref="A3:S7" totalsRowShown="0" headerRowDxfId="110" dataDxfId="109">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{29F43501-CD9F-B44B-A5D1-9D851BC153E9}" name="tblAircraft" displayName="tblAircraft" ref="A3:S7" totalsRowShown="0" headerRowDxfId="115" dataDxfId="114">
   <autoFilter ref="A3:S7" xr:uid="{29F43501-CD9F-B44B-A5D1-9D851BC153E9}"/>
   <tableColumns count="19">
-    <tableColumn id="16" xr3:uid="{4159BB87-D686-954D-A88B-D4B4FC063647}" name="Aircraft ID" dataDxfId="108"/>
-    <tableColumn id="19" xr3:uid="{31A98D46-8645-3E47-A491-098D389FB963}" name="Manufacturer ID" dataDxfId="107"/>
-    <tableColumn id="18" xr3:uid="{D8C620DC-9E63-2E47-90FC-0631C99DD68D}" name="Variant ID" dataDxfId="106"/>
-    <tableColumn id="1" xr3:uid="{C88ECEE8-7952-FC42-BF42-B491BCF2B032}" name="Aircraft" dataDxfId="105"/>
-    <tableColumn id="2" xr3:uid="{0C8FCC8C-2C6A-3244-92BE-CC5E97E74C4A}" name="Simulator" dataDxfId="104"/>
-    <tableColumn id="3" xr3:uid="{30EDD00F-BF35-2E41-AC5D-DEBC1C0B6195}" name="Developer" dataDxfId="103"/>
-    <tableColumn id="4" xr3:uid="{2A5668BE-FA09-6644-AE1F-F5D89D40772A}" name="Aircraft Type" dataDxfId="102"/>
-    <tableColumn id="5" xr3:uid="{6A0F49AA-768A-6C40-97E8-1F024B8185B8}" name="Systems Depth" dataDxfId="101">
+    <tableColumn id="16" xr3:uid="{4159BB87-D686-954D-A88B-D4B4FC063647}" name="Aircraft ID" dataDxfId="113"/>
+    <tableColumn id="19" xr3:uid="{31A98D46-8645-3E47-A491-098D389FB963}" name="Manufacturer ID" dataDxfId="112"/>
+    <tableColumn id="18" xr3:uid="{D8C620DC-9E63-2E47-90FC-0631C99DD68D}" name="Variant ID" dataDxfId="111"/>
+    <tableColumn id="1" xr3:uid="{C88ECEE8-7952-FC42-BF42-B491BCF2B032}" name="Aircraft" dataDxfId="110"/>
+    <tableColumn id="2" xr3:uid="{0C8FCC8C-2C6A-3244-92BE-CC5E97E74C4A}" name="Simulator (Legacy)" dataDxfId="109"/>
+    <tableColumn id="3" xr3:uid="{30EDD00F-BF35-2E41-AC5D-DEBC1C0B6195}" name="Developer (Legacy)" dataDxfId="108"/>
+    <tableColumn id="4" xr3:uid="{2A5668BE-FA09-6644-AE1F-F5D89D40772A}" name="Aircraft Type" dataDxfId="107"/>
+    <tableColumn id="5" xr3:uid="{6A0F49AA-768A-6C40-97E8-1F024B8185B8}" name="Systems Depth" dataDxfId="106">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tblAircraft[[#This Row],[Aircraft ID]],tblSystemsDepth[Aircraft ID],tblSystemsDepth[Systems Depth Score],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{3D0A9F48-F300-E64F-B143-A311E788A8AE}" name="Flight Model Quality" dataDxfId="100"/>
-    <tableColumn id="7" xr3:uid="{A3939B06-A303-6347-920E-ED99075575A7}" name="Update Frequency" dataDxfId="99"/>
-    <tableColumn id="8" xr3:uid="{B253B3DC-A893-4744-8ED4-F4AB018E5100}" name="User Rating" dataDxfId="98"/>
-    <tableColumn id="9" xr3:uid="{7A914067-B537-6C41-B3D9-772A9645DAFE}" name="Release Date" dataDxfId="97"/>
-    <tableColumn id="10" xr3:uid="{029A08CC-A646-2D4F-A2EF-FB9B440D00C0}" name="Status" dataDxfId="96"/>
-    <tableColumn id="11" xr3:uid="{34D44A71-E5CB-F244-9994-5A7D7A5278DE}" name="Source" dataDxfId="95"/>
-    <tableColumn id="12" xr3:uid="{DC4FA8B6-1BC0-E94D-90D3-B57FA7D7C052}" name="Last Updated" dataDxfId="94"/>
-    <tableColumn id="13" xr3:uid="{CDA9DB88-4020-9C43-8A90-D5E0CBE43D53}" name="Update Method" dataDxfId="93"/>
-    <tableColumn id="17" xr3:uid="{808DC6CE-955B-8F4A-B9BC-9C8369B451D6}" name="Update Tool" dataDxfId="92"/>
-    <tableColumn id="14" xr3:uid="{364258FB-0EBA-5545-A4B2-ED1255EBD6FF}" name="Updater Generation" dataDxfId="91"/>
-    <tableColumn id="15" xr3:uid="{DF72689F-59E7-8B4C-9A6F-1B2921ED86E2}" name="Notes" dataDxfId="90"/>
+    <tableColumn id="6" xr3:uid="{3D0A9F48-F300-E64F-B143-A311E788A8AE}" name="Flight Model Quality" dataDxfId="105"/>
+    <tableColumn id="7" xr3:uid="{A3939B06-A303-6347-920E-ED99075575A7}" name="Update Frequency" dataDxfId="104"/>
+    <tableColumn id="8" xr3:uid="{B253B3DC-A893-4744-8ED4-F4AB018E5100}" name="User Rating" dataDxfId="103"/>
+    <tableColumn id="9" xr3:uid="{7A914067-B537-6C41-B3D9-772A9645DAFE}" name="Release Date" dataDxfId="102"/>
+    <tableColumn id="10" xr3:uid="{029A08CC-A646-2D4F-A2EF-FB9B440D00C0}" name="Status" dataDxfId="101"/>
+    <tableColumn id="11" xr3:uid="{34D44A71-E5CB-F244-9994-5A7D7A5278DE}" name="Source" dataDxfId="100"/>
+    <tableColumn id="12" xr3:uid="{DC4FA8B6-1BC0-E94D-90D3-B57FA7D7C052}" name="Last Updated" dataDxfId="99"/>
+    <tableColumn id="13" xr3:uid="{CDA9DB88-4020-9C43-8A90-D5E0CBE43D53}" name="Update Method" dataDxfId="98"/>
+    <tableColumn id="17" xr3:uid="{808DC6CE-955B-8F4A-B9BC-9C8369B451D6}" name="Update Tool" dataDxfId="97"/>
+    <tableColumn id="14" xr3:uid="{364258FB-0EBA-5545-A4B2-ED1255EBD6FF}" name="Updater Generation" dataDxfId="96"/>
+    <tableColumn id="15" xr3:uid="{DF72689F-59E7-8B4C-9A6F-1B2921ED86E2}" name="Notes" dataDxfId="95"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4D75FEAF-B89C-8246-9656-64270FCF13ED}" name="tblAircraftVariants" displayName="tblAircraftVariants" ref="A3:F9" totalsRowShown="0" headerRowDxfId="89" dataDxfId="88">
-  <autoFilter ref="A3:F9" xr:uid="{4D75FEAF-B89C-8246-9656-64270FCF13ED}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{13FE2D4A-EF65-AD49-A6F6-5ADEB0960999}" name="Variant ID" dataDxfId="87"/>
-    <tableColumn id="2" xr3:uid="{5D3B5CE7-B17D-9F41-9F9C-37E621E2406E}" name="Aircraft ID" dataDxfId="86"/>
-    <tableColumn id="3" xr3:uid="{CE1CB680-53C6-1F47-A244-299208BF6D6D}" name="Aircraft" dataDxfId="85">
-      <calculatedColumnFormula>_xlfn.XLOOKUP(B4,tblAircraft[Aircraft ID],tblAircraft[Aircraft],"")</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="4" xr3:uid="{5F624EC0-01EB-214A-BE82-F1FEBD7B2F54}" name="Simulator" dataDxfId="84">
-      <calculatedColumnFormula>_xlfn.XLOOKUP(B4,tblAircraft[Aircraft ID],tblAircraft[Simulator],"")</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="5" xr3:uid="{4811740A-0E07-DE48-AAA7-9F0CBA8131A1}" name="Variant" dataDxfId="83"/>
-    <tableColumn id="6" xr3:uid="{089C1491-BCB4-DC43-A644-5AFC43CBC6F2}" name="Notes" dataDxfId="82"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{BA62EC28-7F8A-6D4E-993A-F4DB246E1765}" name="Table14" displayName="Table14" ref="A3:E5" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+  <autoFilter ref="A3:E5" xr:uid="{BA62EC28-7F8A-6D4E-993A-F4DB246E1765}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{AA6C0D88-605E-5040-9198-0ABC1DCE5C5F}" name="Product ID" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{F16082DF-F373-064E-ABF8-F11C90E6518A}" name="Product Name"/>
+    <tableColumn id="3" xr3:uid="{58B021D0-CD0A-5D40-8A89-E343AD7D25CE}" name="Aircraft ID" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{28B85A3E-3588-F643-9F51-BEFFB39E408F}" name="Simulator" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{2CFB5BC1-1ED7-B047-8364-17A4D9C7E86A}" name="Notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{421B205D-37CE-124D-9AC1-3CA5DC199627}" name="tblEngines" displayName="tblEngines" ref="A3:E8" totalsRowShown="0" headerRowDxfId="81" dataDxfId="80">
-  <autoFilter ref="A3:E8" xr:uid="{421B205D-37CE-124D-9AC1-3CA5DC199627}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{E3EEBAB2-726E-964D-BE8D-1FB7F670A053}" name="Table16" displayName="Table16" ref="A3:E6" totalsRowShown="0">
+  <autoFilter ref="A3:E6" xr:uid="{E3EEBAB2-726E-964D-BE8D-1FB7F670A053}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{9CF07036-AD8A-BF4E-803F-4402A83CC0BC}" name="Engine_ID" dataDxfId="79"/>
-    <tableColumn id="2" xr3:uid="{70E505C8-AA92-2449-A9C7-167F8F23ACFB}" name="Manufacturer" dataDxfId="78"/>
-    <tableColumn id="3" xr3:uid="{408A27B7-FDD3-8C44-9CAE-461218946810}" name="Engine Model" dataDxfId="77"/>
-    <tableColumn id="4" xr3:uid="{37E623C3-3A6D-4E46-942B-9BF3046677D8}" name="Engine Type" dataDxfId="76"/>
-    <tableColumn id="5" xr3:uid="{84948E00-9B85-6C4E-9920-C6429A63FE03}" name="Notes" dataDxfId="75"/>
+    <tableColumn id="1" xr3:uid="{1D0CBCC4-76D3-5E41-A39B-DFCF668687FB}" name="Product Developer ID"/>
+    <tableColumn id="2" xr3:uid="{FE3CD982-9D45-9149-B0AA-A3E6C37876FB}" name="Product ID"/>
+    <tableColumn id="3" xr3:uid="{704F3A98-3771-5144-ADA3-5D07D0D8CE9D}" name="Developer ID"/>
+    <tableColumn id="4" xr3:uid="{D6F1B894-250C-1148-9CBC-4DD613EFD99E}" name="Role"/>
+    <tableColumn id="5" xr3:uid="{80FA0C58-C9A6-8F48-8439-6C40971F2CFC}" name="Notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{94031BC5-15F9-6B4D-AE4C-32C4037123FA}" name="tblVariantEngines" displayName="tblVariantEngines" ref="A3:F8" totalsRowShown="0" headerRowDxfId="74" dataDxfId="73">
-  <autoFilter ref="A3:F8" xr:uid="{94031BC5-15F9-6B4D-AE4C-32C4037123FA}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{5E295C5D-9DB5-844F-9323-F1CD80762DBC}" name="Variant Engine ID" dataDxfId="72"/>
-    <tableColumn id="2" xr3:uid="{B64C8FE6-DF8B-8045-AD7E-4A9F97CA730B}" name="Variant ID" dataDxfId="71"/>
-    <tableColumn id="3" xr3:uid="{47F4F640-4D5A-B946-BA6C-B96953A79904}" name="Engine ID " dataDxfId="70"/>
-    <tableColumn id="4" xr3:uid="{8CAC22F5-34A9-BF4F-AE9B-45FA9850CB1E}" name="Variant" dataDxfId="69">
-      <calculatedColumnFormula>_xlfn.XLOOKUP(tblVariantEngines[[#This Row],[Variant ID]],tblAircraftVariants[Variant ID],tblAircraftVariants[Variant],"")</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="5" xr3:uid="{96283967-4785-A24B-8AC6-E3A49A46EA78}" name="Engine Model " dataDxfId="68">
-      <calculatedColumnFormula>_xlfn.XLOOKUP(C4,Engines_DB!$A$4:$A$100,Engines_DB!$C$4:$C$100,"")</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="6" xr3:uid="{4A40909E-D524-AF42-9D6D-515F3F3963D5}" name="Notes" dataDxfId="67"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{51427A46-ED3D-014F-B0D6-FAFC52AEC65C}" name="Table17" displayName="Table17" ref="A3:D4" insertRow="1" totalsRowShown="0">
+  <autoFilter ref="A3:D4" xr:uid="{51427A46-ED3D-014F-B0D6-FAFC52AEC65C}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{FE79BE94-97CD-5746-B638-107B6E974872}" name="Product Variant ID"/>
+    <tableColumn id="2" xr3:uid="{702E6BDC-808B-A24D-A681-1E9CDB6C6D46}" name="Product ID"/>
+    <tableColumn id="3" xr3:uid="{1DFBC25B-3DF7-0148-88E7-54DBEE0272BA}" name="Variant ID"/>
+    <tableColumn id="4" xr3:uid="{6071C0B4-B920-914F-BA2F-6ECC08127A6E}" name="Notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{0301F975-F2F2-5D43-AAAF-94C3D5A2D8E0}" name="tblAircraftConfigurations" displayName="tblAircraftConfigurations" ref="A3:G7" totalsRowShown="0" headerRowDxfId="66" dataDxfId="65">
-  <autoFilter ref="A3:G7" xr:uid="{0301F975-F2F2-5D43-AAAF-94C3D5A2D8E0}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{596C6310-2F74-E84B-B088-7EE294BD9ECA}" name="Configuration ID" dataDxfId="64"/>
-    <tableColumn id="2" xr3:uid="{F377D330-30E0-9642-AA9D-B2BF8E05CA67}" name="Variant ID" dataDxfId="63"/>
-    <tableColumn id="3" xr3:uid="{EEA61D3A-7D3A-8D4E-B8D1-1CECA34F0770}" name="Aircraft ID" dataDxfId="62">
-      <calculatedColumnFormula>IF(tblAircraftConfigurations[[#This Row],[Variant ID]]="","",_xlfn.XLOOKUP(tblAircraftConfigurations[[#This Row],[Variant ID]],tblAircraftVariants[Variant ID],tblAircraftVariants[Aircraft ID],""))</calculatedColumnFormula>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4D75FEAF-B89C-8246-9656-64270FCF13ED}" name="tblAircraftVariants" displayName="tblAircraftVariants" ref="A3:F9" totalsRowShown="0" headerRowDxfId="94" dataDxfId="93">
+  <autoFilter ref="A3:F9" xr:uid="{4D75FEAF-B89C-8246-9656-64270FCF13ED}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{13FE2D4A-EF65-AD49-A6F6-5ADEB0960999}" name="Variant ID" dataDxfId="92"/>
+    <tableColumn id="2" xr3:uid="{5D3B5CE7-B17D-9F41-9F9C-37E621E2406E}" name="Aircraft ID" dataDxfId="91"/>
+    <tableColumn id="3" xr3:uid="{CE1CB680-53C6-1F47-A244-299208BF6D6D}" name="Aircraft" dataDxfId="90">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(B4,tblAircraft[Aircraft ID],tblAircraft[Aircraft],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{C6BCBE01-EA68-A448-818C-6E9AF2022FE5}" name="Aircraft" dataDxfId="61">
-      <calculatedColumnFormula>IF(tblAircraftConfigurations[[#This Row],[Aircraft ID]]="","",_xlfn.XLOOKUP(tblAircraftConfigurations[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Aircraft],""))</calculatedColumnFormula>
+    <tableColumn id="4" xr3:uid="{5F624EC0-01EB-214A-BE82-F1FEBD7B2F54}" name="Simulator" dataDxfId="89">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(B4,tblAircraft[Aircraft ID],tblAircraft[Simulator (Legacy)],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{0204D856-C495-7044-94A7-8151A77DD052}" name="Simulator" dataDxfId="60">
-      <calculatedColumnFormula>IF(tblAircraftConfigurations[[#This Row],[Aircraft ID]]="","",_xlfn.XLOOKUP(tblAircraftConfigurations[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator],""))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="6" xr3:uid="{42C00E7C-CF6E-F540-AA4E-802164AB0482}" name="Configuration Name" dataDxfId="59"/>
-    <tableColumn id="7" xr3:uid="{FBF2B8E3-DB8D-5641-81C1-6D74707867D0}" name="Notes" dataDxfId="58"/>
+    <tableColumn id="5" xr3:uid="{4811740A-0E07-DE48-AAA7-9F0CBA8131A1}" name="Variant" dataDxfId="88"/>
+    <tableColumn id="6" xr3:uid="{089C1491-BCB4-DC43-A644-5AFC43CBC6F2}" name="Notes" dataDxfId="87"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{63B5D24B-73F5-1641-866F-955C5B4232DF}" name="tblSystemsDepth" displayName="tblSystemsDepth" ref="A3:N7" totalsRowShown="0" headerRowDxfId="57" dataDxfId="56">
-  <autoFilter ref="A3:N7" xr:uid="{63B5D24B-73F5-1641-866F-955C5B4232DF}"/>
-  <tableColumns count="14">
-    <tableColumn id="12" xr3:uid="{71838FF8-8EA3-E145-839C-E770AD0A1825}" name="Evaluation ID" dataDxfId="55"/>
-    <tableColumn id="13" xr3:uid="{830E8BF7-B2BB-AA48-8DD3-7A53BCE99354}" name="Evaluation Sope" dataDxfId="54"/>
-    <tableColumn id="1" xr3:uid="{1CDFBD3B-AC1F-8E40-AD5A-7D32EB0461D8}" name="Aircraft ID" dataDxfId="53"/>
-    <tableColumn id="14" xr3:uid="{89E6CB87-B930-4D4B-9CFF-8F51F5B3D448}" name="Variant ID" dataDxfId="52"/>
-    <tableColumn id="15" xr3:uid="{1846A538-2482-4D4F-B0CD-625030C3A885}" name="Variant" dataDxfId="51">
-      <calculatedColumnFormula>IF(tblSystemsDepth[[#This Row],[Variant ID]]="","",_xlfn.XLOOKUP(tblSystemsDepth[[#This Row],[Variant ID]],tblAircraftVariants[Variant ID],tblAircraftVariants[Variant],""))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="2" xr3:uid="{EFF66939-2B24-8942-AC75-55E8E3512C09}" name="Aircraft" dataDxfId="50">
-      <calculatedColumnFormula>_xlfn.XLOOKUP(tblSystemsDepth[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Aircraft],"")</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="3" xr3:uid="{1A3DB43D-D852-2F42-B2E3-BCD34D59544E}" name="Simulator" dataDxfId="49">
-      <calculatedColumnFormula>_xlfn.XLOOKUP(tblSystemsDepth[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator],"")</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="4" xr3:uid="{FD4E0C00-EB23-D643-ACDC-C68FE92C1F14}" name="Electrical Systems" dataDxfId="48"/>
-    <tableColumn id="5" xr3:uid="{D0D57CB5-2B06-BA41-87E1-9C741B94C9BA}" name="Hydraulic / Pneumatic Systems" dataDxfId="47"/>
-    <tableColumn id="6" xr3:uid="{104E682F-6DC8-854D-A154-5FBA7DEBB578}" name="FMS / Navigation Depth" dataDxfId="46"/>
-    <tableColumn id="7" xr3:uid="{AE16E340-1AC8-6C48-A766-6D329DEFEBE0}" name="Failures / Abnormal Procedures" dataDxfId="45"/>
-    <tableColumn id="8" xr3:uid="{64436D13-11E2-3743-8A88-349F63F3B07A}" name="Procedural Fidelity" dataDxfId="44"/>
-    <tableColumn id="9" xr3:uid="{FF6DA7CD-FDAF-2547-A6E9-9BF3BA532FE3}" name="Systems Depth Score" dataDxfId="43">
-      <calculatedColumnFormula>IF(COUNT(tblSystemsDepth[[#This Row],[Electrical Systems]]:tblSystemsDepth[[#This Row],[Procedural Fidelity]])=0,"",ROUND(SUM(tblSystemsDepth[[#This Row],[Electrical Systems]]:tblSystemsDepth[[#This Row],[Procedural Fidelity]])/(COUNT(tblSystemsDepth[[#This Row],[Electrical Systems]]:tblSystemsDepth[[#This Row],[Procedural Fidelity]])*20)*100,0))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="11" xr3:uid="{24257476-02E0-CC46-A27E-C70E64D998A8}" name="Date Verified" dataDxfId="42">
-      <calculatedColumnFormula>TODAY()</calculatedColumnFormula>
-    </tableColumn>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{421B205D-37CE-124D-9AC1-3CA5DC199627}" name="tblEngines" displayName="tblEngines" ref="A3:E8" totalsRowShown="0" headerRowDxfId="86" dataDxfId="85">
+  <autoFilter ref="A3:E8" xr:uid="{421B205D-37CE-124D-9AC1-3CA5DC199627}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{9CF07036-AD8A-BF4E-803F-4402A83CC0BC}" name="Engine_ID" dataDxfId="84"/>
+    <tableColumn id="2" xr3:uid="{70E505C8-AA92-2449-A9C7-167F8F23ACFB}" name="Manufacturer" dataDxfId="83"/>
+    <tableColumn id="3" xr3:uid="{408A27B7-FDD3-8C44-9CAE-461218946810}" name="Engine Model" dataDxfId="82"/>
+    <tableColumn id="4" xr3:uid="{37E623C3-3A6D-4E46-942B-9BF3046677D8}" name="Engine Type" dataDxfId="81"/>
+    <tableColumn id="5" xr3:uid="{84948E00-9B85-6C4E-9920-C6429A63FE03}" name="Notes" dataDxfId="80"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{2C709437-1283-944D-BA35-6A0090DBFC2A}" name="tblEvaluationSources" displayName="tblEvaluationSources" ref="A3:G13" totalsRowShown="0" headerRowDxfId="41" dataDxfId="40">
-  <autoFilter ref="A3:G13" xr:uid="{2C709437-1283-944D-BA35-6A0090DBFC2A}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{373931B1-12C6-EA45-9488-3CC9CC170B8A}" name="Evaluation Source ID" dataDxfId="39"/>
-    <tableColumn id="2" xr3:uid="{7A4336C9-AD77-5749-AD56-6746F090A352}" name="Evaluation ID" dataDxfId="38"/>
-    <tableColumn id="3" xr3:uid="{CC4C0828-0EFF-E94E-84AA-E2590D186F3E}" name="Source ID" dataDxfId="37"/>
-    <tableColumn id="6" xr3:uid="{19934B5E-6937-ED40-8637-7B3C0A0FCD04}" name="Aircraft" dataDxfId="36">
-      <calculatedColumnFormula>_xlfn.XLOOKUP(tblEvaluationSources[[#This Row],[Evaluation ID]],tblSystemsDepth[Evaluation ID],tblSystemsDepth[Aircraft],"")</calculatedColumnFormula>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{94031BC5-15F9-6B4D-AE4C-32C4037123FA}" name="tblVariantEngines" displayName="tblVariantEngines" ref="A3:F8" totalsRowShown="0" headerRowDxfId="79" dataDxfId="78">
+  <autoFilter ref="A3:F8" xr:uid="{94031BC5-15F9-6B4D-AE4C-32C4037123FA}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{5E295C5D-9DB5-844F-9323-F1CD80762DBC}" name="Variant Engine ID" dataDxfId="77"/>
+    <tableColumn id="2" xr3:uid="{B64C8FE6-DF8B-8045-AD7E-4A9F97CA730B}" name="Variant ID" dataDxfId="76"/>
+    <tableColumn id="3" xr3:uid="{47F4F640-4D5A-B946-BA6C-B96953A79904}" name="Engine ID " dataDxfId="75"/>
+    <tableColumn id="4" xr3:uid="{8CAC22F5-34A9-BF4F-AE9B-45FA9850CB1E}" name="Variant" dataDxfId="74">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(tblVariantEngines[[#This Row],[Variant ID]],tblAircraftVariants[Variant ID],tblAircraftVariants[Variant],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{8B58A9D1-5D0A-5A43-9F0D-FD63879B5104}" name="Source Name" dataDxfId="35">
-      <calculatedColumnFormula>_xlfn.XLOOKUP(tblEvaluationSources[[#This Row],[Source ID]],tblSources[Source ID],tblSources[Source Name],"")</calculatedColumnFormula>
+    <tableColumn id="5" xr3:uid="{96283967-4785-A24B-8AC6-E3A49A46EA78}" name="Engine Model " dataDxfId="73">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(C4,Engines_DB!$A$4:$A$100,Engines_DB!$C$4:$C$100,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{C96A00CF-D76A-8D4D-937F-6484B2249F72}" name="Evidence Role" dataDxfId="34"/>
-    <tableColumn id="5" xr3:uid="{60EE9860-EE6C-5845-9129-4E5C6D8DA919}" name="Notes" dataDxfId="33"/>
+    <tableColumn id="6" xr3:uid="{4A40909E-D524-AF42-9D6D-515F3F3963D5}" name="Notes" dataDxfId="72"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{76DE734F-5104-7649-A8A0-8325D3E9D528}" name="tblAvionics" displayName="tblAvionics" ref="A3:F20" totalsRowShown="0" headerRowDxfId="32" dataDxfId="31">
-  <autoFilter ref="A3:F20" xr:uid="{76DE734F-5104-7649-A8A0-8325D3E9D528}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{8B02509B-77BE-A244-8E95-67E9875FD8A4}" name="Avionics ID" dataDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{FAD56923-8BBD-E349-A02D-D480703FE180}" name="Developer / Manufacturer" dataDxfId="29"/>
-    <tableColumn id="3" xr3:uid="{702DD557-8925-8F4C-9C15-32A33EAA4453}" name="Avionics Type" dataDxfId="28"/>
-    <tableColumn id="4" xr3:uid="{FFA2D378-D7FA-7040-99E5-90F161F2D109}" name="System / Model" dataDxfId="27"/>
-    <tableColumn id="5" xr3:uid="{60CDEF54-08D6-714B-95D6-A1B24C928431}" name="Version / Generation" dataDxfId="26"/>
-    <tableColumn id="6" xr3:uid="{43E29A70-C46E-A54D-A76F-34E730126823}" name="Notes" dataDxfId="25"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{0301F975-F2F2-5D43-AAAF-94C3D5A2D8E0}" name="tblAircraftConfigurations" displayName="tblAircraftConfigurations" ref="A3:G7" totalsRowShown="0" headerRowDxfId="71" dataDxfId="70">
+  <autoFilter ref="A3:G7" xr:uid="{0301F975-F2F2-5D43-AAAF-94C3D5A2D8E0}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{596C6310-2F74-E84B-B088-7EE294BD9ECA}" name="Configuration ID" dataDxfId="69"/>
+    <tableColumn id="2" xr3:uid="{F377D330-30E0-9642-AA9D-B2BF8E05CA67}" name="Variant ID" dataDxfId="68"/>
+    <tableColumn id="3" xr3:uid="{EEA61D3A-7D3A-8D4E-B8D1-1CECA34F0770}" name="Aircraft ID" dataDxfId="67">
+      <calculatedColumnFormula>IF(tblAircraftConfigurations[[#This Row],[Variant ID]]="","",_xlfn.XLOOKUP(tblAircraftConfigurations[[#This Row],[Variant ID]],tblAircraftVariants[Variant ID],tblAircraftVariants[Aircraft ID],""))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{C6BCBE01-EA68-A448-818C-6E9AF2022FE5}" name="Aircraft" dataDxfId="66">
+      <calculatedColumnFormula>IF(tblAircraftConfigurations[[#This Row],[Aircraft ID]]="","",_xlfn.XLOOKUP(tblAircraftConfigurations[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Aircraft],""))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{0204D856-C495-7044-94A7-8151A77DD052}" name="Simulator" dataDxfId="65">
+      <calculatedColumnFormula>IF(tblAircraftConfigurations[[#This Row],[Aircraft ID]]="","",_xlfn.XLOOKUP(tblAircraftConfigurations[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator (Legacy)],""))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{42C00E7C-CF6E-F540-AA4E-802164AB0482}" name="Configuration Name" dataDxfId="64"/>
+    <tableColumn id="7" xr3:uid="{FBF2B8E3-DB8D-5641-81C1-6D74707867D0}" name="Notes" dataDxfId="63"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4921,6 +5124,437 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A2688B2-2111-1C4B-8FDD-FE1BC4B22EEA}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="29.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="22.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.1640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23.33203125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="10.83203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>4</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>5</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>243</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56944C86-8734-414C-8D6C-E04854327A28}">
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.83203125" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="10.83203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="21" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="str">
+        <f>_xlfn.XLOOKUP(tblVariantEngines[[#This Row],[Variant ID]],tblAircraftVariants[Variant ID],tblAircraftVariants[Variant],"")</f>
+        <v>777-200ER</v>
+      </c>
+      <c r="E4" s="1" t="str">
+        <f>_xlfn.XLOOKUP(C4,Engines_DB!$A$4:$A$100,Engines_DB!$C$4:$C$100,"")</f>
+        <v>GE90-90B</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2</v>
+      </c>
+      <c r="D5" s="1" t="str">
+        <f>_xlfn.XLOOKUP(tblVariantEngines[[#This Row],[Variant ID]],tblAircraftVariants[Variant ID],tblAircraftVariants[Variant],"")</f>
+        <v>777-300ER</v>
+      </c>
+      <c r="E5" s="1" t="str">
+        <f>_xlfn.XLOOKUP(C5,Engines_DB!$A$4:$A$100,Engines_DB!$C$4:$C$100,"")</f>
+        <v>GE90-115BL</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="str">
+        <f>_xlfn.XLOOKUP(tblVariantEngines[[#This Row],[Variant ID]],tblAircraftVariants[Variant ID],tblAircraftVariants[Variant],"")</f>
+        <v>777F</v>
+      </c>
+      <c r="E6" s="1" t="str">
+        <f>_xlfn.XLOOKUP(C6,Engines_DB!$A$4:$A$100,Engines_DB!$C$4:$C$100,"")</f>
+        <v>GE90-110B1L</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>4</v>
+      </c>
+      <c r="B7" s="1">
+        <v>4</v>
+      </c>
+      <c r="C7" s="1">
+        <v>4</v>
+      </c>
+      <c r="D7" s="1" t="str">
+        <f>_xlfn.XLOOKUP(tblVariantEngines[[#This Row],[Variant ID]],tblAircraftVariants[Variant ID],tblAircraftVariants[Variant],"")</f>
+        <v>SR20  G3</v>
+      </c>
+      <c r="E7" s="1" t="str">
+        <f>_xlfn.XLOOKUP(C7,Engines_DB!$A$4:$A$100,Engines_DB!$C$4:$C$100,"")</f>
+        <v>IO-360-ES</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>5</v>
+      </c>
+      <c r="B8" s="1">
+        <v>5</v>
+      </c>
+      <c r="C8" s="1">
+        <v>5</v>
+      </c>
+      <c r="D8" s="1" t="str">
+        <f>_xlfn.XLOOKUP(tblVariantEngines[[#This Row],[Variant ID]],tblAircraftVariants[Variant ID],tblAircraftVariants[Variant],"")</f>
+        <v>DA50 RG</v>
+      </c>
+      <c r="E8" s="1" t="str">
+        <f>_xlfn.XLOOKUP(C8,Engines_DB!$A$4:$A$100,Engines_DB!$C$4:$C$100,"")</f>
+        <v>CD-300</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B8" xr:uid="{BDC18CE9-C2D8-4F4D-B001-7808C8B74403}">
+      <formula1>Variant_ID</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:C8" xr:uid="{93637B54-5FFA-7843-A139-95EAABA72BDD}">
+      <formula1>Engine_ID</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4905CEA3-F4F4-AF44-BEBD-AEAB56EC1A55}">
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="17" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.33203125" style="1" customWidth="1"/>
+    <col min="2" max="5" width="17" style="1"/>
+    <col min="6" max="6" width="34" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="17" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1">
+        <f>IF(tblAircraftConfigurations[[#This Row],[Variant ID]]="","",_xlfn.XLOOKUP(tblAircraftConfigurations[[#This Row],[Variant ID]],tblAircraftVariants[Variant ID],tblAircraftVariants[Aircraft ID],""))</f>
+        <v>1</v>
+      </c>
+      <c r="D4" s="16">
+        <f>IF(tblAircraftConfigurations[[#This Row],[Aircraft ID]]="","",_xlfn.XLOOKUP(tblAircraftConfigurations[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Aircraft],""))</f>
+        <v>777</v>
+      </c>
+      <c r="E4" s="1" t="str">
+        <f>IF(tblAircraftConfigurations[[#This Row],[Aircraft ID]]="","",_xlfn.XLOOKUP(tblAircraftConfigurations[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator (Legacy)],""))</f>
+        <v>X-Plane 12</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1">
+        <v>4</v>
+      </c>
+      <c r="C5" s="1">
+        <f>IF(tblAircraftConfigurations[[#This Row],[Variant ID]]="","",_xlfn.XLOOKUP(tblAircraftConfigurations[[#This Row],[Variant ID]],tblAircraftVariants[Variant ID],tblAircraftVariants[Aircraft ID],""))</f>
+        <v>2</v>
+      </c>
+      <c r="D5" s="16" t="str">
+        <f>IF(tblAircraftConfigurations[[#This Row],[Aircraft ID]]="","",_xlfn.XLOOKUP(tblAircraftConfigurations[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Aircraft],""))</f>
+        <v>SR20</v>
+      </c>
+      <c r="E5" s="1" t="str">
+        <f>IF(tblAircraftConfigurations[[#This Row],[Aircraft ID]]="","",_xlfn.XLOOKUP(tblAircraftConfigurations[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator (Legacy)],""))</f>
+        <v>X-Plane 12</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1">
+        <v>5</v>
+      </c>
+      <c r="C6" s="1">
+        <f>IF(tblAircraftConfigurations[[#This Row],[Variant ID]]="","",_xlfn.XLOOKUP(tblAircraftConfigurations[[#This Row],[Variant ID]],tblAircraftVariants[Variant ID],tblAircraftVariants[Aircraft ID],""))</f>
+        <v>3</v>
+      </c>
+      <c r="D6" s="16" t="str">
+        <f>IF(tblAircraftConfigurations[[#This Row],[Aircraft ID]]="","",_xlfn.XLOOKUP(tblAircraftConfigurations[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Aircraft],""))</f>
+        <v>DA50</v>
+      </c>
+      <c r="E6" s="1" t="str">
+        <f>IF(tblAircraftConfigurations[[#This Row],[Aircraft ID]]="","",_xlfn.XLOOKUP(tblAircraftConfigurations[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator (Legacy)],""))</f>
+        <v>X-Plane 12</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>4</v>
+      </c>
+      <c r="B7" s="1">
+        <v>6</v>
+      </c>
+      <c r="C7" s="1">
+        <f>IF(tblAircraftConfigurations[[#This Row],[Variant ID]]="","",_xlfn.XLOOKUP(tblAircraftConfigurations[[#This Row],[Variant ID]],tblAircraftVariants[Variant ID],tblAircraftVariants[Aircraft ID],""))</f>
+        <v>4</v>
+      </c>
+      <c r="D7" s="16" t="str">
+        <f>IF(tblAircraftConfigurations[[#This Row],[Aircraft ID]]="","",_xlfn.XLOOKUP(tblAircraftConfigurations[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Aircraft],""))</f>
+        <v>A321</v>
+      </c>
+      <c r="E7" s="1" t="str">
+        <f>IF(tblAircraftConfigurations[[#This Row],[Aircraft ID]]="","",_xlfn.XLOOKUP(tblAircraftConfigurations[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator (Legacy)],""))</f>
+        <v>X-Plane 12</v>
+      </c>
+      <c r="F7" t="s">
+        <v>286</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>287</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B7" xr:uid="{312D2B53-AC9F-A341-9B6F-2E523E947221}">
+      <formula1>Variant_ID</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{438658DD-099B-2141-BACF-EFFE3F1CB921}">
   <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
@@ -4944,24 +5578,24 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>97</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>27</v>
@@ -4970,25 +5604,25 @@
         <v>20</v>
       </c>
       <c r="H3" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.3">
@@ -5007,7 +5641,7 @@
         <v>777</v>
       </c>
       <c r="G4" s="1" t="str">
-        <f>_xlfn.XLOOKUP(tblSystemsDepth[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator],"")</f>
+        <f>_xlfn.XLOOKUP(tblSystemsDepth[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator (Legacy)],"")</f>
         <v>X-Plane 12</v>
       </c>
       <c r="H4" s="1">
@@ -5038,7 +5672,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C5" s="1">
         <v>2</v>
@@ -5055,7 +5689,7 @@
         <v>SR20</v>
       </c>
       <c r="G5" s="1" t="str">
-        <f>_xlfn.XLOOKUP(tblSystemsDepth[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator],"")</f>
+        <f>_xlfn.XLOOKUP(tblSystemsDepth[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator (Legacy)],"")</f>
         <v>X-Plane 12</v>
       </c>
       <c r="H5" s="1">
@@ -5086,7 +5720,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C6" s="1">
         <v>3</v>
@@ -5103,7 +5737,7 @@
         <v>DA50</v>
       </c>
       <c r="G6" s="1" t="str">
-        <f>_xlfn.XLOOKUP(tblSystemsDepth[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator],"")</f>
+        <f>_xlfn.XLOOKUP(tblSystemsDepth[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator (Legacy)],"")</f>
         <v>X-Plane 12</v>
       </c>
       <c r="H6" s="1">
@@ -5134,7 +5768,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C7" s="1">
         <v>4</v>
@@ -5151,7 +5785,7 @@
         <v>A321</v>
       </c>
       <c r="G7" s="1" t="str">
-        <f>_xlfn.XLOOKUP(tblSystemsDepth[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator],"")</f>
+        <f>_xlfn.XLOOKUP(tblSystemsDepth[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator (Legacy)],"")</f>
         <v>X-Plane 12</v>
       </c>
       <c r="H7" s="1">
@@ -5200,7 +5834,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9FDB576-BB92-6B4E-B1CA-75A02BF3F966}">
   <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="20.33203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -5217,30 +5851,30 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>27</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="18" x14ac:dyDescent="0.25">
@@ -5262,10 +5896,10 @@
         <v>FlightFactor 777 Ultimate Introduction Bulletin</v>
       </c>
       <c r="F4" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="G4" s="13" t="s">
         <v>144</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -5287,10 +5921,10 @@
         <v>FlightFactor 777 Systems Manual</v>
       </c>
       <c r="F5" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="G5" s="13" t="s">
         <v>146</v>
-      </c>
-      <c r="G5" s="13" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -5312,10 +5946,10 @@
         <v>FlightFactor 777 Cockpit Guide</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -5337,10 +5971,10 @@
         <v>FlightFactor 777 Automatic Interactive Procedures</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="17" x14ac:dyDescent="0.25">
@@ -5362,10 +5996,10 @@
         <v>TorqueSim SR20 Airplane Information Manual</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="17" x14ac:dyDescent="0.25">
@@ -5387,10 +6021,10 @@
         <v>TorqueSim SR20 Garmin Perspective Direct Testing</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -5454,10 +6088,10 @@
         <v>ToLiss A321 Direct Flight Evaluation</v>
       </c>
       <c r="F12" s="29" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G12" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -5479,10 +6113,10 @@
         <v>ToLiss A321 Developer Documentation</v>
       </c>
       <c r="F13" s="31" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G13" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
   </sheetData>
@@ -5504,7 +6138,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71C4C4B6-8AF1-5F43-AF51-C8B79B79BD01}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -5513,7 +6147,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0242A9D0-54F7-BF44-9182-083A900A43BA}">
   <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="28.6640625" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
@@ -5525,27 +6159,27 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -5553,16 +6187,16 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="F4" s="9" t="s">
         <v>176</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -5570,19 +6204,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="6" t="s">
         <v>221</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -5590,16 +6224,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D6" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="F6" s="6" t="s">
         <v>247</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -5607,16 +6241,16 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D7" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="F7" s="6" t="s">
         <v>260</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -5624,16 +6258,16 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D8" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="F8" s="6" t="s">
         <v>270</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -5641,16 +6275,16 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="F9" s="6" t="s">
         <v>273</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -5658,16 +6292,16 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D10" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="F10" s="6" t="s">
         <v>275</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -5675,16 +6309,16 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D11" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="F11" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -5692,16 +6326,16 @@
         <v>9</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D12" t="s">
+        <v>297</v>
+      </c>
+      <c r="F12" t="s">
         <v>298</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="D12" t="s">
-        <v>299</v>
-      </c>
-      <c r="F12" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -5709,16 +6343,16 @@
         <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D13" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -5726,16 +6360,16 @@
         <v>11</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -5743,16 +6377,16 @@
         <v>12</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -5760,16 +6394,16 @@
         <v>13</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -5777,16 +6411,16 @@
         <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -5794,16 +6428,16 @@
         <v>15</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -5811,16 +6445,16 @@
         <v>16</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -5828,16 +6462,16 @@
         <v>17</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -5854,7 +6488,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3316813-0790-7D46-908B-8AAC76593AF1}">
   <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="25.6640625" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
@@ -5869,30 +6503,30 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="G3" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -5914,7 +6548,7 @@
         <v>FlightFactor EFB</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -5936,10 +6570,10 @@
         <v>Garmin Perspective</v>
       </c>
       <c r="F5" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="G5" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -5961,10 +6595,10 @@
         <v>Garmin G1000 / X1000</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -5986,10 +6620,10 @@
         <v>777 Flight Management System (FMS/FMC)</v>
       </c>
       <c r="F7" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="G7" s="6" t="s">
         <v>262</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -6011,10 +6645,10 @@
         <v>777 Primary Flight &amp; Navigation Display System</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -6036,10 +6670,10 @@
         <v>777 Center Multifunction Display System</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -6061,10 +6695,10 @@
         <v>777 Autoflight / Flight Director System</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -6086,10 +6720,10 @@
         <v>Airbus A321 Flight Management and Guidance System (FMGS)</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -6111,10 +6745,10 @@
         <v>Airbus A321 Autopilot / Flight Director System</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -6136,10 +6770,10 @@
         <v>Airbus A321 Primary Flight / Navigation Display System</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -6161,10 +6795,10 @@
         <v>Airbus A321 ECAM Engine Warning / System Display System</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -6186,10 +6820,10 @@
         <v>Airbus A321 ACARS / CPDLC System</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -6211,10 +6845,10 @@
         <v>ToLiss A321 Electronic Flight Bag (EFB)</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -6236,10 +6870,10 @@
         <v>Airbus A321 Weather Radar System</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -6261,10 +6895,10 @@
         <v>Airbus A321 Traffic Alert and Collision Avoidance System (TCAS)</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -6286,10 +6920,10 @@
         <v>Airbus A321 Terrain Awareness and Warning System (TAWS/EGPWS)</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -6311,10 +6945,10 @@
         <v>Airbus A321 GPS / Navigation System</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
   </sheetData>
@@ -6335,7 +6969,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DE896E9-A113-6647-BB6C-700F0EDCD240}">
   <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="23.33203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -6346,57 +6980,57 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="16" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>181</v>
-      </c>
       <c r="C3" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E3" s="18" t="s">
         <v>27</v>
       </c>
       <c r="F3" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="G3" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="H3" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="O3" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="H3" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>184</v>
-      </c>
       <c r="P3" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="16" x14ac:dyDescent="0.25">
@@ -6451,7 +7085,7 @@
         <v>100</v>
       </c>
       <c r="P4" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
@@ -6506,7 +7140,7 @@
         <v>97</v>
       </c>
       <c r="P5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
@@ -6561,7 +7195,7 @@
         <v>95</v>
       </c>
       <c r="P6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
@@ -6616,7 +7250,7 @@
         <v>100</v>
       </c>
       <c r="P7" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
@@ -6671,7 +7305,7 @@
         <v>100</v>
       </c>
       <c r="P8" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
@@ -6726,7 +7360,7 @@
         <v>100</v>
       </c>
       <c r="P9" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
@@ -6781,7 +7415,7 @@
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
@@ -6836,7 +7470,7 @@
         <v>100</v>
       </c>
       <c r="P11" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
@@ -6891,7 +7525,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
@@ -6946,7 +7580,7 @@
         <v>100</v>
       </c>
       <c r="P13" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
@@ -7001,7 +7635,7 @@
         <v>100</v>
       </c>
       <c r="P14" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
@@ -7056,7 +7690,7 @@
         <v>100</v>
       </c>
       <c r="P15" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
@@ -7111,7 +7745,7 @@
         <v>99</v>
       </c>
       <c r="P16" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.2">
@@ -7166,7 +7800,7 @@
         <v>96</v>
       </c>
       <c r="P17" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.2">
@@ -7274,7 +7908,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.2">
@@ -7329,7 +7963,7 @@
         <v>98</v>
       </c>
       <c r="P20" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -7374,37 +8008,37 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76080090-4783-4549-A31F-9270447A629B}">
   <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="29.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="16" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>27</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="16" x14ac:dyDescent="0.25">
@@ -7426,10 +8060,10 @@
         <v>FlightFactor EFB</v>
       </c>
       <c r="F4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="16" x14ac:dyDescent="0.25">
@@ -7451,10 +8085,10 @@
         <v>FlightFactor EFB</v>
       </c>
       <c r="F5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="16" x14ac:dyDescent="0.25">
@@ -7476,10 +8110,10 @@
         <v>FlightFactor EFB</v>
       </c>
       <c r="F6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="16" x14ac:dyDescent="0.25">
@@ -7501,10 +8135,10 @@
         <v>FlightFactor EFB</v>
       </c>
       <c r="F7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -7526,10 +8160,10 @@
         <v>Garmin Perspective</v>
       </c>
       <c r="F8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -7551,10 +8185,10 @@
         <v>Garmin Perspective</v>
       </c>
       <c r="F9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="16" x14ac:dyDescent="0.25">
@@ -7576,10 +8210,10 @@
         <v>Garmin G1000 / X1000</v>
       </c>
       <c r="F10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -7601,10 +8235,10 @@
         <v>Garmin G1000 / X1000</v>
       </c>
       <c r="F11" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G11" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -7626,10 +8260,10 @@
         <v>777 Flight Management System (FMS/FMC)</v>
       </c>
       <c r="F12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G12" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -7651,10 +8285,10 @@
         <v>777 Flight Management System (FMS/FMC)</v>
       </c>
       <c r="F13" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G13" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -7676,10 +8310,10 @@
         <v>777 Flight Management System (FMS/FMC)</v>
       </c>
       <c r="F14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G14" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
@@ -7701,10 +8335,10 @@
         <v>777 Flight Management System (FMS/FMC)</v>
       </c>
       <c r="F15" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G15" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
   </sheetData>
@@ -7726,7 +8360,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB003820-4260-4745-8B85-717E7F127C1F}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D596CE2F-6182-3F4E-9C62-D1574891EDB8}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -7735,7 +8378,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CA0DE01-FBA5-A14F-950F-9E0853DAC316}">
   <dimension ref="A1:N128"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -7759,24 +8402,24 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="D3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D3" s="15" t="s">
-        <v>97</v>
-      </c>
       <c r="E3" s="15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F3" s="15" t="s">
         <v>27</v>
@@ -7785,25 +8428,25 @@
         <v>20</v>
       </c>
       <c r="H3" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="J3" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="I3" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="J3" s="15" t="s">
+      <c r="K3" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="K3" s="15" t="s">
+      <c r="L3" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="M3" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="N3" s="15" t="s">
         <v>84</v>
-      </c>
-      <c r="L3" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="M3" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="N3" s="15" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="18" x14ac:dyDescent="0.25">
@@ -7821,21 +8464,21 @@
         <v>777-200ER</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F4" s="20">
         <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Aircraft],"")</f>
         <v>777</v>
       </c>
       <c r="G4" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator],"")</f>
+        <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator (Legacy)],"")</f>
         <v>X-Plane 12</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K4" s="17">
         <v>46274</v>
@@ -7844,7 +8487,7 @@
         <v>46274</v>
       </c>
       <c r="N4" s="15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="18" x14ac:dyDescent="0.25">
@@ -7859,33 +8502,33 @@
         <v/>
       </c>
       <c r="E5" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F5" s="20">
         <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Aircraft],"")</f>
         <v>777</v>
       </c>
       <c r="G5" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator],"")</f>
+        <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator (Legacy)],"")</f>
         <v>X-Plane 12</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K5" s="17">
         <v>46274</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M5" s="17">
         <v>46274</v>
       </c>
       <c r="N5" s="15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="18" x14ac:dyDescent="0.25">
@@ -7903,33 +8546,33 @@
         <v>777-200ER</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F6" s="20">
         <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Aircraft],"")</f>
         <v>777</v>
       </c>
       <c r="G6" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator],"")</f>
+        <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator (Legacy)],"")</f>
         <v>X-Plane 12</v>
       </c>
       <c r="H6" s="15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K6" s="17">
         <v>46274</v>
       </c>
       <c r="L6" s="15" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M6" s="17">
         <v>46274</v>
       </c>
       <c r="N6" s="15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="18" x14ac:dyDescent="0.25">
@@ -7947,33 +8590,33 @@
         <v>777-300ER</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F7" s="20">
         <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Aircraft],"")</f>
         <v>777</v>
       </c>
       <c r="G7" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator],"")</f>
+        <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator (Legacy)],"")</f>
         <v>X-Plane 12</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K7" s="17">
         <v>46274</v>
       </c>
       <c r="L7" s="15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="M7" s="17">
         <v>46274</v>
       </c>
       <c r="N7" s="15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="18" x14ac:dyDescent="0.25">
@@ -7991,33 +8634,33 @@
         <v>777F</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F8" s="20">
         <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Aircraft],"")</f>
         <v>777</v>
       </c>
       <c r="G8" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator],"")</f>
+        <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator (Legacy)],"")</f>
         <v>X-Plane 12</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K8" s="17">
         <v>46274</v>
       </c>
       <c r="L8" s="15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="M8" s="17">
         <v>46274</v>
       </c>
       <c r="N8" s="15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="18" x14ac:dyDescent="0.25">
@@ -8032,33 +8675,33 @@
         <v/>
       </c>
       <c r="E9" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F9" s="20">
         <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Aircraft],"")</f>
         <v>777</v>
       </c>
       <c r="G9" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator],"")</f>
+        <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator (Legacy)],"")</f>
         <v>X-Plane 12</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K9" s="17">
         <v>46274</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M9" s="17">
         <v>46274</v>
       </c>
       <c r="N9" s="15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="18" x14ac:dyDescent="0.25">
@@ -8077,26 +8720,26 @@
         <v>777</v>
       </c>
       <c r="G10" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator],"")</f>
+        <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator (Legacy)],"")</f>
         <v>X-Plane 12</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K10" s="17">
         <v>46274</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M10" s="17">
         <v>46274</v>
       </c>
       <c r="N10" s="15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="18" x14ac:dyDescent="0.25">
@@ -8115,26 +8758,26 @@
         <v>777</v>
       </c>
       <c r="G11" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator],"")</f>
+        <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator (Legacy)],"")</f>
         <v>X-Plane 12</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K11" s="17">
         <v>46274</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M11" s="17">
         <v>46274</v>
       </c>
       <c r="N11" s="15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="18" x14ac:dyDescent="0.25">
@@ -8153,26 +8796,26 @@
         <v>777</v>
       </c>
       <c r="G12" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator],"")</f>
+        <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator (Legacy)],"")</f>
         <v>X-Plane 12</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K12" s="17">
         <v>46274</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M12" s="17">
         <v>46274</v>
       </c>
       <c r="N12" s="15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="18" x14ac:dyDescent="0.25">
@@ -8187,33 +8830,33 @@
         <v/>
       </c>
       <c r="E13" s="15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F13" s="20">
         <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Aircraft],"")</f>
         <v>777</v>
       </c>
       <c r="G13" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator],"")</f>
+        <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator (Legacy)],"")</f>
         <v>X-Plane 12</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K13" s="17">
         <v>46275</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="M13" s="17">
         <v>46275</v>
       </c>
       <c r="N13" s="15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="18" x14ac:dyDescent="0.25">
@@ -8231,33 +8874,33 @@
         <v>SR20  G3</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F14" s="20" t="str">
         <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Aircraft],"")</f>
         <v>SR20</v>
       </c>
       <c r="G14" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator],"")</f>
+        <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator (Legacy)],"")</f>
         <v>X-Plane 12</v>
       </c>
       <c r="H14" s="15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="K14" s="17">
         <v>46275</v>
       </c>
       <c r="L14" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M14" s="17">
         <v>46275</v>
       </c>
       <c r="N14" s="15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="18" x14ac:dyDescent="0.25">
@@ -8275,34 +8918,34 @@
         <v>SR20  G3</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F15" s="20" t="str">
         <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Aircraft],"")</f>
         <v>SR20</v>
       </c>
       <c r="G15" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator],"")</f>
+        <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator (Legacy)],"")</f>
         <v>X-Plane 12</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K15" s="17">
         <f ca="1">TODAY()</f>
-        <v>46286</v>
+        <v>46289</v>
       </c>
       <c r="L15" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="M15" s="17">
         <v>46276</v>
       </c>
       <c r="N15" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="18" x14ac:dyDescent="0.25">
@@ -8325,27 +8968,27 @@
         <v>DA50</v>
       </c>
       <c r="G16" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator],"")</f>
+        <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator (Legacy)],"")</f>
         <v>X-Plane 12</v>
       </c>
       <c r="H16" s="24" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J16" s="24"/>
       <c r="K16" s="26">
         <v>46276</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="M16" s="17">
         <v>46276</v>
       </c>
       <c r="N16" s="24" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="18" x14ac:dyDescent="0.25">
@@ -8363,34 +9006,34 @@
         <v>DA50 RG</v>
       </c>
       <c r="E17" s="24" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F17" s="25" t="str">
         <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Aircraft],"")</f>
         <v>DA50</v>
       </c>
       <c r="G17" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator],"")</f>
+        <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator (Legacy)],"")</f>
         <v>X-Plane 12</v>
       </c>
       <c r="H17" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="J17" s="24"/>
       <c r="K17" s="26">
         <v>46276</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="M17" s="17">
         <v>46276</v>
       </c>
       <c r="N17" s="24" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="18" x14ac:dyDescent="0.25">
@@ -8408,38 +9051,38 @@
         <v>DA50 RG</v>
       </c>
       <c r="E18" s="24" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F18" s="25" t="str">
         <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Aircraft],"")</f>
         <v>DA50</v>
       </c>
       <c r="G18" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator],"")</f>
+        <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator (Legacy)],"")</f>
         <v>X-Plane 12</v>
       </c>
       <c r="H18" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I18" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="J18" s="28" t="s">
         <v>257</v>
-      </c>
-      <c r="J18" s="28" t="s">
-        <v>258</v>
       </c>
       <c r="K18" s="26">
         <f ca="1">TODAY()</f>
-        <v>46286</v>
+        <v>46289</v>
       </c>
       <c r="L18" s="24" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="M18" s="26">
         <f ca="1">TODAY()</f>
-        <v>46286</v>
+        <v>46289</v>
       </c>
       <c r="N18" s="24" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="18" x14ac:dyDescent="0.25">
@@ -8457,36 +9100,36 @@
         <v>777-200ER</v>
       </c>
       <c r="E19" s="24" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F19" s="25">
         <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Aircraft],"")</f>
         <v>777</v>
       </c>
       <c r="G19" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator],"")</f>
+        <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator (Legacy)],"")</f>
         <v>X-Plane 12</v>
       </c>
       <c r="H19" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J19" s="24"/>
       <c r="K19" s="26">
         <f ca="1">TODAY()</f>
-        <v>46286</v>
+        <v>46289</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="M19" s="26">
         <f ca="1">TODAY()</f>
-        <v>46286</v>
+        <v>46289</v>
       </c>
       <c r="N19" s="24" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="18" x14ac:dyDescent="0.25">
@@ -8504,36 +9147,36 @@
         <v>A321-200</v>
       </c>
       <c r="E20" s="31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F20" s="32" t="str">
         <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Aircraft],"")</f>
         <v>A321</v>
       </c>
       <c r="G20" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator],"")</f>
+        <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator (Legacy)],"")</f>
         <v>X-Plane 12</v>
       </c>
       <c r="H20" s="31" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="J20" s="31"/>
       <c r="K20" s="33">
         <f ca="1">TODAY()</f>
-        <v>46286</v>
+        <v>46289</v>
       </c>
       <c r="L20" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="M20" s="33">
         <f ca="1">TODAY()</f>
-        <v>46286</v>
+        <v>46289</v>
       </c>
       <c r="N20" s="31" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="18" x14ac:dyDescent="0.25">
@@ -8551,36 +9194,36 @@
         <v>A321-200</v>
       </c>
       <c r="E21" s="31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F21" s="32" t="str">
         <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Aircraft],"")</f>
         <v>A321</v>
       </c>
       <c r="G21" s="9" t="str">
-        <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator],"")</f>
+        <f>_xlfn.XLOOKUP(tblSources[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator (Legacy)],"")</f>
         <v>X-Plane 12</v>
       </c>
       <c r="H21" s="31" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I21" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="J21" s="31"/>
       <c r="K21" s="33">
         <f ca="1">TODAY()</f>
-        <v>46286</v>
+        <v>46289</v>
       </c>
       <c r="L21" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="M21" s="33">
         <f ca="1">TODAY()</f>
-        <v>46286</v>
+        <v>46289</v>
       </c>
       <c r="N21" s="31" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
@@ -9022,7 +9665,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{413CD778-8246-7046-89B1-B6CC4BF38021}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -9031,16 +9674,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB003820-4260-4745-8B85-717E7F127C1F}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A80A8C2F-000F-FC49-9FFB-F0B98744F453}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -9049,7 +9683,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2118DCC-F251-9D48-8017-7987BFA146AB}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -9058,16 +9692,74 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{634763C7-82C2-8646-9BA5-E6F61DF053F5}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="22.5" customWidth="1"/>
+    <col min="3" max="3" width="30.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="16" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B3" t="s">
+        <v>358</v>
+      </c>
+      <c r="C3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>365</v>
+      </c>
+      <c r="C5" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>296</v>
+      </c>
+      <c r="C6" t="s">
+        <v>359</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89ADF72F-ADBE-3E47-86B7-45321074E4A8}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -9076,7 +9768,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{628CD998-AE40-184A-9872-A4A8C916F6F3}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -9085,7 +9777,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{614CFDD2-B148-3946-8135-B3A9B2C8DBEF}">
   <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
@@ -9186,7 +9878,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2AE9672-3906-584B-BCEF-9C8891BC5807}">
   <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
@@ -9346,7 +10038,68 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A3AD335-10BA-C846-98C4-1938C854F1A8}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="20.5" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="16384" width="20.5" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>4</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7901750-A9C2-D646-94E7-606639C9D6CA}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -9355,7 +10108,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DAEAB16-029C-7A48-8E04-6B379CEDBF9C}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -9364,7 +10117,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B29B4685-C664-E94F-B0DA-1105513273F7}">
   <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
@@ -9381,25 +10134,25 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -9410,22 +10163,22 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -9433,39 +10186,39 @@
         <v>22</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -9473,19 +10226,19 @@
         <v>23</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -9493,203 +10246,142 @@
         <v>24</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C8" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="G9" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="I10" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="I11" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="I12" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="I13" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A3AD335-10BA-C846-98C4-1938C854F1A8}">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="20.5" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="16384" width="20.5" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>1</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>2</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>3</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>4</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>283</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -9732,61 +10424,61 @@
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>20</v>
+        <v>348</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>15</v>
       </c>
       <c r="K3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="R3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="Q3" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="R3" s="1" t="s">
+      <c r="S3" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
@@ -9803,20 +10495,20 @@
         <v>23</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H4" s="1">
         <f>_xlfn.XLOOKUP(tblAircraft[[#This Row],[Aircraft ID]],tblSystemsDepth[Aircraft ID],tblSystemsDepth[Systems Depth Score],"")</f>
         <v>97</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
@@ -9827,23 +10519,23 @@
         <v>2</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H5" s="1">
         <f>_xlfn.XLOOKUP(tblAircraft[[#This Row],[Aircraft ID]],tblSystemsDepth[Aircraft ID],tblSystemsDepth[Systems Depth Score],"")</f>
         <v>98</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
@@ -9854,16 +10546,16 @@
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H6" s="1">
         <f>_xlfn.XLOOKUP(tblAircraft[[#This Row],[Aircraft ID]],tblSystemsDepth[Aircraft ID],tblSystemsDepth[Systems Depth Score],"")</f>
@@ -9881,16 +10573,16 @@
         <v>6</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H7" s="1">
         <f>_xlfn.XLOOKUP(tblAircraft[[#This Row],[Aircraft ID]],tblSystemsDepth[Aircraft ID],tblSystemsDepth[Systems Depth Score],"")</f>
@@ -9948,6 +10640,213 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B28DDE3B-F0C3-804F-A87F-07501588C11C}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.1640625" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="35.6640625" customWidth="1"/>
+    <col min="5" max="5" width="37.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.25">
+      <c r="A1" s="36" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="19" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="19" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="E4" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="19" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>355</v>
+      </c>
+      <c r="C5" s="1">
+        <v>6</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="E5" t="s">
+        <v>370</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A03BB6DC-FF18-E846-8023-92FC21AC3AC6}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="20.1640625" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" customWidth="1"/>
+    <col min="3" max="3" width="13.1640625" customWidth="1"/>
+    <col min="4" max="4" width="16.5" customWidth="1"/>
+    <col min="5" max="5" width="46.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="B3" t="s">
+        <v>350</v>
+      </c>
+      <c r="C3" t="s">
+        <v>356</v>
+      </c>
+      <c r="D3" t="s">
+        <v>362</v>
+      </c>
+      <c r="E3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>363</v>
+      </c>
+      <c r="E4" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5" t="s">
+        <v>367</v>
+      </c>
+      <c r="E5" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6" t="s">
+        <v>363</v>
+      </c>
+      <c r="E6" t="s">
+        <v>369</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B6104DF-4A66-3244-B80F-0C160313BDA1}">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="25.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" customWidth="1"/>
+    <col min="3" max="3" width="20.1640625" customWidth="1"/>
+    <col min="4" max="4" width="17.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="8" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="B3" t="s">
+        <v>350</v>
+      </c>
+      <c r="C3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69FBE426-1707-5443-9733-49CB8F2A68DA}">
   <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
@@ -9963,15 +10862,15 @@
   <sheetData>
     <row r="1" spans="1:6" ht="23" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>27</v>
@@ -9980,10 +10879,10 @@
         <v>20</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="22" x14ac:dyDescent="0.3">
@@ -9998,11 +10897,11 @@
         <v>777</v>
       </c>
       <c r="D4" s="7" t="str">
-        <f>_xlfn.XLOOKUP(B4,tblAircraft[Aircraft ID],tblAircraft[Simulator],"")</f>
+        <f>_xlfn.XLOOKUP(B4,tblAircraft[Aircraft ID],tblAircraft[Simulator (Legacy)],"")</f>
         <v>X-Plane 12</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F4" s="1"/>
     </row>
@@ -10018,11 +10917,11 @@
         <v>777</v>
       </c>
       <c r="D5" s="7" t="str">
-        <f>_xlfn.XLOOKUP(B5,tblAircraft[Aircraft ID],tblAircraft[Simulator],"")</f>
+        <f>_xlfn.XLOOKUP(B5,tblAircraft[Aircraft ID],tblAircraft[Simulator (Legacy)],"")</f>
         <v>X-Plane 12</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F5" s="1"/>
     </row>
@@ -10038,11 +10937,11 @@
         <v>777</v>
       </c>
       <c r="D6" s="7" t="str">
-        <f>_xlfn.XLOOKUP(B6,tblAircraft[Aircraft ID],tblAircraft[Simulator],"")</f>
+        <f>_xlfn.XLOOKUP(B6,tblAircraft[Aircraft ID],tblAircraft[Simulator (Legacy)],"")</f>
         <v>X-Plane 12</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F6" s="1"/>
     </row>
@@ -10058,14 +10957,14 @@
         <v>SR20</v>
       </c>
       <c r="D7" s="7" t="str">
-        <f>_xlfn.XLOOKUP(B7,tblAircraft[Aircraft ID],tblAircraft[Simulator],"")</f>
+        <f>_xlfn.XLOOKUP(B7,tblAircraft[Aircraft ID],tblAircraft[Simulator (Legacy)],"")</f>
         <v>X-Plane 12</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="F7" s="6" t="s">
         <v>211</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="22" x14ac:dyDescent="0.3">
@@ -10080,14 +10979,14 @@
         <v>DA50</v>
       </c>
       <c r="D8" s="7" t="str">
-        <f>_xlfn.XLOOKUP(B8,tblAircraft[Aircraft ID],tblAircraft[Simulator],"")</f>
+        <f>_xlfn.XLOOKUP(B8,tblAircraft[Aircraft ID],tblAircraft[Simulator (Legacy)],"")</f>
         <v>X-Plane 12</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="F8" s="6" t="s">
         <v>237</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="22" x14ac:dyDescent="0.3">
@@ -10102,14 +11001,14 @@
         <v>A321</v>
       </c>
       <c r="D9" s="7" t="str">
-        <f>_xlfn.XLOOKUP(B9,tblAircraft[Aircraft ID],tblAircraft[Simulator],"")</f>
+        <f>_xlfn.XLOOKUP(B9,tblAircraft[Aircraft ID],tblAircraft[Simulator (Legacy)],"")</f>
         <v>X-Plane 12</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
   </sheetData>
@@ -10118,435 +11017,4 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A2688B2-2111-1C4B-8FDD-FE1BC4B22EEA}">
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="22.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="29.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="22.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="22.1640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.33203125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="10.83203125" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>1</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>2</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>3</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>4</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>5</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>244</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56944C86-8734-414C-8D6C-E04854327A28}">
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="25.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="20.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.83203125" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="10.83203125" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="21" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>1</v>
-      </c>
-      <c r="B4" s="1">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1">
-        <v>1</v>
-      </c>
-      <c r="D4" s="1" t="str">
-        <f>_xlfn.XLOOKUP(tblVariantEngines[[#This Row],[Variant ID]],tblAircraftVariants[Variant ID],tblAircraftVariants[Variant],"")</f>
-        <v>777-200ER</v>
-      </c>
-      <c r="E4" s="1" t="str">
-        <f>_xlfn.XLOOKUP(C4,Engines_DB!$A$4:$A$100,Engines_DB!$C$4:$C$100,"")</f>
-        <v>GE90-90B</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>2</v>
-      </c>
-      <c r="B5" s="1">
-        <v>2</v>
-      </c>
-      <c r="C5" s="1">
-        <v>2</v>
-      </c>
-      <c r="D5" s="1" t="str">
-        <f>_xlfn.XLOOKUP(tblVariantEngines[[#This Row],[Variant ID]],tblAircraftVariants[Variant ID],tblAircraftVariants[Variant],"")</f>
-        <v>777-300ER</v>
-      </c>
-      <c r="E5" s="1" t="str">
-        <f>_xlfn.XLOOKUP(C5,Engines_DB!$A$4:$A$100,Engines_DB!$C$4:$C$100,"")</f>
-        <v>GE90-115BL</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>3</v>
-      </c>
-      <c r="B6" s="1">
-        <v>3</v>
-      </c>
-      <c r="C6" s="1">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="str">
-        <f>_xlfn.XLOOKUP(tblVariantEngines[[#This Row],[Variant ID]],tblAircraftVariants[Variant ID],tblAircraftVariants[Variant],"")</f>
-        <v>777F</v>
-      </c>
-      <c r="E6" s="1" t="str">
-        <f>_xlfn.XLOOKUP(C6,Engines_DB!$A$4:$A$100,Engines_DB!$C$4:$C$100,"")</f>
-        <v>GE90-110B1L</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>4</v>
-      </c>
-      <c r="B7" s="1">
-        <v>4</v>
-      </c>
-      <c r="C7" s="1">
-        <v>4</v>
-      </c>
-      <c r="D7" s="1" t="str">
-        <f>_xlfn.XLOOKUP(tblVariantEngines[[#This Row],[Variant ID]],tblAircraftVariants[Variant ID],tblAircraftVariants[Variant],"")</f>
-        <v>SR20  G3</v>
-      </c>
-      <c r="E7" s="1" t="str">
-        <f>_xlfn.XLOOKUP(C7,Engines_DB!$A$4:$A$100,Engines_DB!$C$4:$C$100,"")</f>
-        <v>IO-360-ES</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>5</v>
-      </c>
-      <c r="B8" s="1">
-        <v>5</v>
-      </c>
-      <c r="C8" s="1">
-        <v>5</v>
-      </c>
-      <c r="D8" s="1" t="str">
-        <f>_xlfn.XLOOKUP(tblVariantEngines[[#This Row],[Variant ID]],tblAircraftVariants[Variant ID],tblAircraftVariants[Variant],"")</f>
-        <v>DA50 RG</v>
-      </c>
-      <c r="E8" s="1" t="str">
-        <f>_xlfn.XLOOKUP(C8,Engines_DB!$A$4:$A$100,Engines_DB!$C$4:$C$100,"")</f>
-        <v>CD-300</v>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B8" xr:uid="{BDC18CE9-C2D8-4F4D-B001-7808C8B74403}">
-      <formula1>Variant_ID</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:C8" xr:uid="{93637B54-5FFA-7843-A139-95EAABA72BDD}">
-      <formula1>Engine_ID</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4905CEA3-F4F4-AF44-BEBD-AEAB56EC1A55}">
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="17" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="24.33203125" style="1" customWidth="1"/>
-    <col min="2" max="5" width="17" style="1"/>
-    <col min="6" max="6" width="34" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="17" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>1</v>
-      </c>
-      <c r="B4" s="1">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1">
-        <f>IF(tblAircraftConfigurations[[#This Row],[Variant ID]]="","",_xlfn.XLOOKUP(tblAircraftConfigurations[[#This Row],[Variant ID]],tblAircraftVariants[Variant ID],tblAircraftVariants[Aircraft ID],""))</f>
-        <v>1</v>
-      </c>
-      <c r="D4" s="16">
-        <f>IF(tblAircraftConfigurations[[#This Row],[Aircraft ID]]="","",_xlfn.XLOOKUP(tblAircraftConfigurations[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Aircraft],""))</f>
-        <v>777</v>
-      </c>
-      <c r="E4" s="1" t="str">
-        <f>IF(tblAircraftConfigurations[[#This Row],[Aircraft ID]]="","",_xlfn.XLOOKUP(tblAircraftConfigurations[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator],""))</f>
-        <v>X-Plane 12</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>2</v>
-      </c>
-      <c r="B5" s="1">
-        <v>4</v>
-      </c>
-      <c r="C5" s="1">
-        <f>IF(tblAircraftConfigurations[[#This Row],[Variant ID]]="","",_xlfn.XLOOKUP(tblAircraftConfigurations[[#This Row],[Variant ID]],tblAircraftVariants[Variant ID],tblAircraftVariants[Aircraft ID],""))</f>
-        <v>2</v>
-      </c>
-      <c r="D5" s="16" t="str">
-        <f>IF(tblAircraftConfigurations[[#This Row],[Aircraft ID]]="","",_xlfn.XLOOKUP(tblAircraftConfigurations[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Aircraft],""))</f>
-        <v>SR20</v>
-      </c>
-      <c r="E5" s="1" t="str">
-        <f>IF(tblAircraftConfigurations[[#This Row],[Aircraft ID]]="","",_xlfn.XLOOKUP(tblAircraftConfigurations[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator],""))</f>
-        <v>X-Plane 12</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>3</v>
-      </c>
-      <c r="B6" s="1">
-        <v>5</v>
-      </c>
-      <c r="C6" s="1">
-        <f>IF(tblAircraftConfigurations[[#This Row],[Variant ID]]="","",_xlfn.XLOOKUP(tblAircraftConfigurations[[#This Row],[Variant ID]],tblAircraftVariants[Variant ID],tblAircraftVariants[Aircraft ID],""))</f>
-        <v>3</v>
-      </c>
-      <c r="D6" s="16" t="str">
-        <f>IF(tblAircraftConfigurations[[#This Row],[Aircraft ID]]="","",_xlfn.XLOOKUP(tblAircraftConfigurations[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Aircraft],""))</f>
-        <v>DA50</v>
-      </c>
-      <c r="E6" s="1" t="str">
-        <f>IF(tblAircraftConfigurations[[#This Row],[Aircraft ID]]="","",_xlfn.XLOOKUP(tblAircraftConfigurations[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator],""))</f>
-        <v>X-Plane 12</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>4</v>
-      </c>
-      <c r="B7" s="1">
-        <v>6</v>
-      </c>
-      <c r="C7" s="1">
-        <f>IF(tblAircraftConfigurations[[#This Row],[Variant ID]]="","",_xlfn.XLOOKUP(tblAircraftConfigurations[[#This Row],[Variant ID]],tblAircraftVariants[Variant ID],tblAircraftVariants[Aircraft ID],""))</f>
-        <v>4</v>
-      </c>
-      <c r="D7" s="16" t="str">
-        <f>IF(tblAircraftConfigurations[[#This Row],[Aircraft ID]]="","",_xlfn.XLOOKUP(tblAircraftConfigurations[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Aircraft],""))</f>
-        <v>A321</v>
-      </c>
-      <c r="E7" s="1" t="str">
-        <f>IF(tblAircraftConfigurations[[#This Row],[Aircraft ID]]="","",_xlfn.XLOOKUP(tblAircraftConfigurations[[#This Row],[Aircraft ID]],tblAircraft[Aircraft ID],tblAircraft[Simulator],""))</f>
-        <v>X-Plane 12</v>
-      </c>
-      <c r="F7" t="s">
-        <v>288</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>289</v>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B7" xr:uid="{312D2B53-AC9F-A341-9B6F-2E523E947221}">
-      <formula1>Variant_ID</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
 </file>